--- a/evaluate/result_langchain.xlsx
+++ b/evaluate/result_langchain.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Pycharm\code\Maintenance_Assistance_System\evaluate\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A56420A-CE3D-479C-B846-E33261F35F62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="0" yWindow="420" windowWidth="19987" windowHeight="13860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -4703,12 +4709,12 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -4716,8 +4722,15 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -4763,17 +4776,25 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -4811,7 +4832,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -4845,6 +4866,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -4879,9 +4901,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -5054,11 +5077,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I356"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="8" max="9" width="0" hidden="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5087,7 +5113,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -5101,7 +5127,7 @@
         <v>1046</v>
       </c>
       <c r="E2">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F2">
         <v>1</v>
@@ -5110,13 +5136,13 @@
         <v>1</v>
       </c>
       <c r="H2">
-        <v>0.7007135421371712</v>
+        <v>0.70071354213717119</v>
       </c>
       <c r="I2">
         <v>0.5564531431238906</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -5139,13 +5165,13 @@
         <v>1</v>
       </c>
       <c r="H3">
-        <v>0.5413225797511853</v>
+        <v>0.54132257975118525</v>
       </c>
       <c r="I3">
-        <v>0.6061121592137024</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
+        <v>0.60611215921370243</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -5159,7 +5185,7 @@
         <v>1048</v>
       </c>
       <c r="E4">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F4">
         <v>1</v>
@@ -5171,10 +5197,10 @@
         <v>0.3313112892257874</v>
       </c>
       <c r="I4">
-        <v>0.6073633755421233</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
+        <v>0.60736337554212327</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -5188,7 +5214,7 @@
         <v>1049</v>
       </c>
       <c r="E5">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F5">
         <v>1</v>
@@ -5197,13 +5223,13 @@
         <v>1</v>
       </c>
       <c r="H5">
-        <v>0.280194512043995</v>
+        <v>0.28019451204399498</v>
       </c>
       <c r="I5">
         <v>0.6622661022944063</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -5217,7 +5243,7 @@
         <v>1050</v>
       </c>
       <c r="E6">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F6">
         <v>0.5</v>
@@ -5226,13 +5252,13 @@
         <v>0.625</v>
       </c>
       <c r="H6">
-        <v>0.5847627230360919</v>
+        <v>0.58476272303609189</v>
       </c>
       <c r="I6">
         <v>0.1588674237055939</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -5246,7 +5272,7 @@
         <v>1051</v>
       </c>
       <c r="E7">
-        <v>0.8333333332916666</v>
+        <v>0.83333333329166659</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -5255,13 +5281,13 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>0.6680217174488614</v>
+        <v>0.66802171744886141</v>
       </c>
       <c r="I7">
-        <v>0.4967028436236537</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9">
+        <v>0.49670284362365369</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>15</v>
       </c>
@@ -5284,13 +5310,13 @@
         <v>0</v>
       </c>
       <c r="H8">
-        <v>0.6127694572426445</v>
+        <v>0.61276945724264453</v>
       </c>
       <c r="I8">
-        <v>0.4873369550965357</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
+        <v>0.48733695509653568</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -5316,10 +5342,10 @@
         <v>0</v>
       </c>
       <c r="I9">
-        <v>0.5201806527911668</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
+        <v>0.52018065279116676</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -5333,22 +5359,22 @@
         <v>1054</v>
       </c>
       <c r="E10">
-        <v>0.8333333332916666</v>
+        <v>0.83333333329166659</v>
       </c>
       <c r="F10">
         <v>1</v>
       </c>
       <c r="G10">
-        <v>0.8333333333333334</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="H10">
-        <v>0.549848601366927</v>
+        <v>0.54984860136692704</v>
       </c>
       <c r="I10">
-        <v>0.6819650213477614</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9">
+        <v>0.68196502134776138</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -5371,13 +5397,13 @@
         <v>0</v>
       </c>
       <c r="H11">
-        <v>0.5166129354120628</v>
+        <v>0.51661293541206277</v>
       </c>
       <c r="I11">
-        <v>0.4996554068901508</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9">
+        <v>0.49965540689015081</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -5391,7 +5417,7 @@
         <v>1056</v>
       </c>
       <c r="E12">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F12">
         <v>1</v>
@@ -5400,13 +5426,13 @@
         <v>0.75</v>
       </c>
       <c r="H12">
-        <v>0.4880258343725138</v>
+        <v>0.48802583437251379</v>
       </c>
       <c r="I12">
-        <v>0.8156498653117875</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9">
+        <v>0.81564986531178751</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>20</v>
       </c>
@@ -5420,7 +5446,7 @@
         <v>1057</v>
       </c>
       <c r="E13">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F13">
         <v>1</v>
@@ -5429,13 +5455,13 @@
         <v>1</v>
       </c>
       <c r="H13">
-        <v>0.7021931579689643</v>
+        <v>0.70219315796896431</v>
       </c>
       <c r="I13">
-        <v>0.1204414226733247</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9">
+        <v>0.12044142267332469</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>21</v>
       </c>
@@ -5449,7 +5475,7 @@
         <v>1058</v>
       </c>
       <c r="E14">
-        <v>0.9999999999666667</v>
+        <v>0.99999999996666666</v>
       </c>
       <c r="F14">
         <v>0.5</v>
@@ -5458,13 +5484,13 @@
         <v>0.625</v>
       </c>
       <c r="H14">
-        <v>0.4261567622384728</v>
+        <v>0.42615676223847282</v>
       </c>
       <c r="I14">
         <v>0.3756226610572303</v>
       </c>
     </row>
-    <row r="15" spans="1:9">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>22</v>
       </c>
@@ -5487,13 +5513,13 @@
         <v>1</v>
       </c>
       <c r="H15">
-        <v>0.6637791608746224</v>
+        <v>0.66377916087462241</v>
       </c>
       <c r="I15">
-        <v>0.264207321913707</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9">
+        <v>0.26420732191370699</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>23</v>
       </c>
@@ -5516,13 +5542,13 @@
         <v>1</v>
       </c>
       <c r="H16">
-        <v>0.6486667566251685</v>
+        <v>0.64866675662516848</v>
       </c>
       <c r="I16">
-        <v>0.1731961006106496</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9">
+        <v>0.17319610061064961</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>24</v>
       </c>
@@ -5548,10 +5574,10 @@
         <v>0.5143298100699526</v>
       </c>
       <c r="I17">
-        <v>0.7653464279477579</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9">
+        <v>0.76534642794775787</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>25</v>
       </c>
@@ -5565,22 +5591,22 @@
         <v>1062</v>
       </c>
       <c r="E18">
-        <v>0.5833333333041666</v>
+        <v>0.58333333330416659</v>
       </c>
       <c r="F18">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="G18">
-        <v>0.8888888888888888</v>
+        <v>0.88888888888888884</v>
       </c>
       <c r="H18">
-        <v>0.609842574454687</v>
+        <v>0.60984257445468704</v>
       </c>
       <c r="I18">
-        <v>0.655034858055898</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9">
+        <v>0.65503485805589801</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>26</v>
       </c>
@@ -5594,7 +5620,7 @@
         <v>1063</v>
       </c>
       <c r="E19">
-        <v>0.8333333332916666</v>
+        <v>0.83333333329166659</v>
       </c>
       <c r="F19">
         <v>1</v>
@@ -5603,13 +5629,13 @@
         <v>1</v>
       </c>
       <c r="H19">
-        <v>0.6896467254590088</v>
+        <v>0.68964672545900885</v>
       </c>
       <c r="I19">
-        <v>0.8217700649282544</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9">
+        <v>0.82177006492825444</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>27</v>
       </c>
@@ -5629,16 +5655,16 @@
         <v>1</v>
       </c>
       <c r="G20">
-        <v>0.1666666666666667</v>
+        <v>0.16666666666666671</v>
       </c>
       <c r="H20">
-        <v>0.5924374770506065</v>
+        <v>0.59243747705060645</v>
       </c>
       <c r="I20">
-        <v>0.4373413954975108</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9">
+        <v>0.43734139549751078</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>28</v>
       </c>
@@ -5652,7 +5678,7 @@
         <v>1065</v>
       </c>
       <c r="E21">
-        <v>0.9999999999666667</v>
+        <v>0.99999999996666666</v>
       </c>
       <c r="F21">
         <v>1</v>
@@ -5661,13 +5687,13 @@
         <v>1</v>
       </c>
       <c r="H21">
-        <v>0.5235489002190851</v>
+        <v>0.52354890021908507</v>
       </c>
       <c r="I21">
-        <v>0.9506520728815583</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9">
+        <v>0.95065207288155829</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>29</v>
       </c>
@@ -5681,7 +5707,7 @@
         <v>1066</v>
       </c>
       <c r="E22">
-        <v>0.9999999999666667</v>
+        <v>0.99999999996666666</v>
       </c>
       <c r="F22">
         <v>1</v>
@@ -5690,13 +5716,13 @@
         <v>1</v>
       </c>
       <c r="H22">
-        <v>0.56058937757203</v>
+        <v>0.56058937757202998</v>
       </c>
       <c r="I22">
-        <v>0.754133986630748</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9">
+        <v>0.75413398663074804</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>30</v>
       </c>
@@ -5719,13 +5745,13 @@
         <v>0</v>
       </c>
       <c r="H23">
-        <v>0.3298447436628519</v>
+        <v>0.32984474366285188</v>
       </c>
       <c r="I23">
-        <v>0.2735227263687736</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9">
+        <v>0.27352272636877362</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>31</v>
       </c>
@@ -5748,13 +5774,13 @@
         <v>0</v>
       </c>
       <c r="H24">
-        <v>0.5527316527411062</v>
+        <v>0.55273165274110625</v>
       </c>
       <c r="I24">
-        <v>0.1647826161661028</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9">
+        <v>0.16478261616610279</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>32</v>
       </c>
@@ -5777,13 +5803,13 @@
         <v>1</v>
       </c>
       <c r="H25">
-        <v>0.3888334575085773</v>
+        <v>0.38883345750857728</v>
       </c>
       <c r="I25">
-        <v>0.8475394405314698</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9">
+        <v>0.84753944053146979</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>33</v>
       </c>
@@ -5806,13 +5832,13 @@
         <v>1</v>
       </c>
       <c r="H26">
-        <v>0.6460008583983611</v>
+        <v>0.64600085839836108</v>
       </c>
       <c r="I26">
-        <v>0.7144779635318714</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9">
+        <v>0.71447796353187143</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>34</v>
       </c>
@@ -5835,13 +5861,13 @@
         <v>0</v>
       </c>
       <c r="H27">
-        <v>0.6553305792281927</v>
+        <v>0.65533057922819271</v>
       </c>
       <c r="I27">
         <v>0.3371213639521029</v>
       </c>
     </row>
-    <row r="28" spans="1:9">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>35</v>
       </c>
@@ -5864,13 +5890,13 @@
         <v>1</v>
       </c>
       <c r="H28">
-        <v>0.4935049163950065</v>
+        <v>0.49350491639500649</v>
       </c>
       <c r="I28">
-        <v>0.7118348216210401</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9">
+        <v>0.71183482162104006</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>36</v>
       </c>
@@ -5884,22 +5910,22 @@
         <v>1073</v>
       </c>
       <c r="E29">
-        <v>0.5833333333041666</v>
+        <v>0.58333333330416659</v>
       </c>
       <c r="F29">
         <v>1</v>
       </c>
       <c r="G29">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="H29">
-        <v>0.4704606138446377</v>
+        <v>0.47046061384463772</v>
       </c>
       <c r="I29">
-        <v>0.5655365439353615</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9">
+        <v>0.56553654393536146</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>37</v>
       </c>
@@ -5913,7 +5939,7 @@
         <v>1074</v>
       </c>
       <c r="E30">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F30">
         <v>1</v>
@@ -5922,13 +5948,13 @@
         <v>1</v>
       </c>
       <c r="H30">
-        <v>0.4461826557967249</v>
+        <v>0.44618265579672489</v>
       </c>
       <c r="I30">
-        <v>0.2990715189795942</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9">
+        <v>0.29907151897959422</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>38</v>
       </c>
@@ -5957,7 +5983,7 @@
         <v>0.640007621931443</v>
       </c>
     </row>
-    <row r="32" spans="1:9">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>39</v>
       </c>
@@ -5980,13 +6006,13 @@
         <v>0</v>
       </c>
       <c r="H32">
-        <v>0.5078933860717438</v>
+        <v>0.50789338607174384</v>
       </c>
       <c r="I32">
-        <v>0.3781701802374964</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9">
+        <v>0.37817018023749638</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>40</v>
       </c>
@@ -6000,22 +6026,22 @@
         <v>1077</v>
       </c>
       <c r="E33">
-        <v>0.9999999999666667</v>
+        <v>0.99999999996666666</v>
       </c>
       <c r="F33">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="G33">
-        <v>0.6153846153846154</v>
+        <v>0.61538461538461542</v>
       </c>
       <c r="H33">
-        <v>0.454360729523768</v>
+        <v>0.45436072952376799</v>
       </c>
       <c r="I33">
-        <v>0.3989039406260672</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9">
+        <v>0.39890394062606721</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>41</v>
       </c>
@@ -6035,13 +6061,13 @@
         <v>1</v>
       </c>
       <c r="G34">
-        <v>0.7272727272727273</v>
+        <v>0.72727272727272729</v>
       </c>
       <c r="H34">
-        <v>0.3946353755866072</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9">
+        <v>0.39463537558660722</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>42</v>
       </c>
@@ -6055,7 +6081,7 @@
         <v>1079</v>
       </c>
       <c r="E35">
-        <v>0.9999999999666667</v>
+        <v>0.99999999996666666</v>
       </c>
       <c r="F35">
         <v>1</v>
@@ -6064,10 +6090,10 @@
         <v>1</v>
       </c>
       <c r="H35">
-        <v>0.999999507037837</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9">
+        <v>0.99999950703783702</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>43</v>
       </c>
@@ -6090,13 +6116,13 @@
         <v>0</v>
       </c>
       <c r="H36">
-        <v>0.5121945520469885</v>
+        <v>0.51219455204698849</v>
       </c>
       <c r="I36">
-        <v>0.490467484415968</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9">
+        <v>0.49046748441596799</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>44</v>
       </c>
@@ -6119,13 +6145,13 @@
         <v>0</v>
       </c>
       <c r="H37">
-        <v>0.4598588847064046</v>
+        <v>0.45985888470640462</v>
       </c>
       <c r="I37">
-        <v>0.5912549368046462</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9">
+        <v>0.59125493680464625</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>45</v>
       </c>
@@ -6139,22 +6165,22 @@
         <v>1082</v>
       </c>
       <c r="E38">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F38">
         <v>1</v>
       </c>
       <c r="G38">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="H38">
-        <v>0.7515245592142016</v>
+        <v>0.75152455921420158</v>
       </c>
       <c r="I38">
-        <v>0.8303373464230147</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9">
+        <v>0.83033734642301471</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>46</v>
       </c>
@@ -6168,22 +6194,22 @@
         <v>1083</v>
       </c>
       <c r="E39">
-        <v>0.9999999999666667</v>
+        <v>0.99999999996666666</v>
       </c>
       <c r="F39">
         <v>1</v>
       </c>
       <c r="G39">
-        <v>0.9166666666666666</v>
+        <v>0.91666666666666663</v>
       </c>
       <c r="H39">
-        <v>0.5222174905420904</v>
+        <v>0.52221749054209043</v>
       </c>
       <c r="I39">
-        <v>0.3565187758418137</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9">
+        <v>0.35651877584181368</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>47</v>
       </c>
@@ -6197,7 +6223,7 @@
         <v>1084</v>
       </c>
       <c r="E40">
-        <v>0.9999999999666667</v>
+        <v>0.99999999996666666</v>
       </c>
       <c r="F40">
         <v>1</v>
@@ -6206,13 +6232,13 @@
         <v>0.75</v>
       </c>
       <c r="H40">
-        <v>0.2931297761226224</v>
+        <v>0.29312977612262242</v>
       </c>
       <c r="I40">
-        <v>0.5633042636584411</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9">
+        <v>0.56330426365844111</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>48</v>
       </c>
@@ -6226,7 +6252,7 @@
         <v>1085</v>
       </c>
       <c r="E41">
-        <v>0.8333333332916666</v>
+        <v>0.83333333329166659</v>
       </c>
       <c r="F41">
         <v>1</v>
@@ -6235,13 +6261,13 @@
         <v>0.5714285714285714</v>
       </c>
       <c r="H41">
-        <v>0.8829132829839155</v>
+        <v>0.88291328298391547</v>
       </c>
       <c r="I41">
-        <v>0.43620468021929</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9">
+        <v>0.43620468021928999</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>49</v>
       </c>
@@ -6255,22 +6281,22 @@
         <v>1086</v>
       </c>
       <c r="E42">
-        <v>0.8333333332916666</v>
+        <v>0.83333333329166659</v>
       </c>
       <c r="F42">
         <v>1</v>
       </c>
       <c r="G42">
-        <v>0.8333333333333334</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="H42">
-        <v>0.4634183888706168</v>
+        <v>0.46341838887061682</v>
       </c>
       <c r="I42">
         <v>0.9330161757562212</v>
       </c>
     </row>
-    <row r="43" spans="1:9">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>50</v>
       </c>
@@ -6293,13 +6319,13 @@
         <v>0.75</v>
       </c>
       <c r="H43">
-        <v>0.7012651898964054</v>
+        <v>0.70126518989640541</v>
       </c>
       <c r="I43">
-        <v>0.2450169677018116</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9">
+        <v>0.24501696770181161</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>51</v>
       </c>
@@ -6313,7 +6339,7 @@
         <v>1088</v>
       </c>
       <c r="E44">
-        <v>0.8333333332916666</v>
+        <v>0.83333333329166659</v>
       </c>
       <c r="F44">
         <v>1</v>
@@ -6322,13 +6348,13 @@
         <v>1</v>
       </c>
       <c r="H44">
-        <v>0.5942294170924042</v>
+        <v>0.59422941709240418</v>
       </c>
       <c r="I44">
-        <v>0.7822520687261039</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9">
+        <v>0.78225206872610387</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>52</v>
       </c>
@@ -6342,7 +6368,7 @@
         <v>1089</v>
       </c>
       <c r="E45">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F45">
         <v>1</v>
@@ -6351,13 +6377,13 @@
         <v>1</v>
       </c>
       <c r="H45">
-        <v>0.5255968322303617</v>
+        <v>0.52559683223036169</v>
       </c>
       <c r="I45">
-        <v>0.4785465581230722</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9">
+        <v>0.47854655812307217</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>53</v>
       </c>
@@ -6371,7 +6397,7 @@
         <v>1090</v>
       </c>
       <c r="E46">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F46">
         <v>1</v>
@@ -6380,13 +6406,13 @@
         <v>1</v>
       </c>
       <c r="H46">
-        <v>0.9038963554754481</v>
+        <v>0.90389635547544811</v>
       </c>
       <c r="I46">
-        <v>0.8688818300490284</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9">
+        <v>0.86888183004902841</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>54</v>
       </c>
@@ -6400,7 +6426,7 @@
         <v>1091</v>
       </c>
       <c r="E47">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F47">
         <v>1</v>
@@ -6409,13 +6435,13 @@
         <v>1</v>
       </c>
       <c r="H47">
-        <v>0.6853203823600029</v>
+        <v>0.68532038236000292</v>
       </c>
       <c r="I47">
-        <v>0.6367939521440942</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9">
+        <v>0.63679395214409418</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>55</v>
       </c>
@@ -6429,7 +6455,7 @@
         <v>1092</v>
       </c>
       <c r="E48">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F48">
         <v>1</v>
@@ -6438,13 +6464,13 @@
         <v>0</v>
       </c>
       <c r="H48">
-        <v>0.5056091952045128</v>
+        <v>0.50560919520451275</v>
       </c>
       <c r="I48">
-        <v>0.6210524066921176</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9">
+        <v>0.62105240669211759</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>56</v>
       </c>
@@ -6467,13 +6493,13 @@
         <v>0</v>
       </c>
       <c r="H49">
-        <v>0.4302003625270859</v>
+        <v>0.43020036252708588</v>
       </c>
       <c r="I49">
-        <v>0.5150203849599063</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9">
+        <v>0.51502038495990632</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>57</v>
       </c>
@@ -6487,7 +6513,7 @@
         <v>1094</v>
       </c>
       <c r="E50">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F50">
         <v>1</v>
@@ -6496,13 +6522,13 @@
         <v>1</v>
       </c>
       <c r="H50">
-        <v>0.5492720114793549</v>
+        <v>0.54927201147935489</v>
       </c>
       <c r="I50">
-        <v>0.6076699649075468</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9">
+        <v>0.60766996490754677</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>58</v>
       </c>
@@ -6516,22 +6542,22 @@
         <v>1095</v>
       </c>
       <c r="E51">
-        <v>0.5833333333041666</v>
+        <v>0.58333333330416659</v>
       </c>
       <c r="F51">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="G51">
         <v>0.375</v>
       </c>
       <c r="H51">
-        <v>0.7735288879201179</v>
+        <v>0.77352888792011787</v>
       </c>
       <c r="I51">
-        <v>0.4212731536598761</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9">
+        <v>0.42127315365987611</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>59</v>
       </c>
@@ -6545,7 +6571,7 @@
         <v>1096</v>
       </c>
       <c r="E52">
-        <v>0.9999999999666667</v>
+        <v>0.99999999996666666</v>
       </c>
       <c r="F52">
         <v>1</v>
@@ -6554,13 +6580,13 @@
         <v>1</v>
       </c>
       <c r="H52">
-        <v>0.6580953428899957</v>
+        <v>0.65809534288999572</v>
       </c>
       <c r="I52">
-        <v>0.5753005013996609</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9">
+        <v>0.57530050139966094</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>60</v>
       </c>
@@ -6574,7 +6600,7 @@
         <v>1097</v>
       </c>
       <c r="E53">
-        <v>0.8333333332916666</v>
+        <v>0.83333333329166659</v>
       </c>
       <c r="F53">
         <v>1</v>
@@ -6586,10 +6612,10 @@
         <v>0.6576277829172783</v>
       </c>
       <c r="I53">
-        <v>0.528263465583342</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9">
+        <v>0.52826346558334203</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>61</v>
       </c>
@@ -6612,13 +6638,13 @@
         <v>0.8125</v>
       </c>
       <c r="H54">
-        <v>0.6155084233584727</v>
+        <v>0.61550842335847267</v>
       </c>
       <c r="I54">
-        <v>0.1679515275172807</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9">
+        <v>0.16795152751728071</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>62</v>
       </c>
@@ -6641,13 +6667,13 @@
         <v>0.75</v>
       </c>
       <c r="H55">
-        <v>0.8226210413964948</v>
+        <v>0.82262104139649483</v>
       </c>
       <c r="I55">
         <v>0.4924412834438977</v>
       </c>
     </row>
-    <row r="56" spans="1:9">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>63</v>
       </c>
@@ -6661,22 +6687,22 @@
         <v>1100</v>
       </c>
       <c r="E56">
-        <v>0.9999999999666667</v>
+        <v>0.99999999996666666</v>
       </c>
       <c r="F56">
         <v>0.8</v>
       </c>
       <c r="G56">
-        <v>0.5555555555555556</v>
+        <v>0.55555555555555558</v>
       </c>
       <c r="H56">
-        <v>0.6300719563109298</v>
+        <v>0.63007195631092983</v>
       </c>
       <c r="I56">
         <v>0.4612131397493428</v>
       </c>
     </row>
-    <row r="57" spans="1:9">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>64</v>
       </c>
@@ -6690,7 +6716,7 @@
         <v>1101</v>
       </c>
       <c r="E57">
-        <v>0.9999999999666667</v>
+        <v>0.99999999996666666</v>
       </c>
       <c r="F57">
         <v>0</v>
@@ -6699,13 +6725,13 @@
         <v>0</v>
       </c>
       <c r="H57">
-        <v>0.717091477100478</v>
+        <v>0.71709147710047805</v>
       </c>
       <c r="I57">
-        <v>0.3779792261200738</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9">
+        <v>0.37797922612007379</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>65</v>
       </c>
@@ -6719,7 +6745,7 @@
         <v>1102</v>
       </c>
       <c r="E58">
-        <v>0.9999999999666667</v>
+        <v>0.99999999996666666</v>
       </c>
       <c r="F58">
         <v>1</v>
@@ -6728,13 +6754,13 @@
         <v>1</v>
       </c>
       <c r="H58">
-        <v>0.7218998920968935</v>
+        <v>0.72189989209689354</v>
       </c>
       <c r="I58">
         <v>0.4432463148790452</v>
       </c>
     </row>
-    <row r="59" spans="1:9">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>66</v>
       </c>
@@ -6748,7 +6774,7 @@
         <v>1103</v>
       </c>
       <c r="E59">
-        <v>0.9999999999666667</v>
+        <v>0.99999999996666666</v>
       </c>
       <c r="F59">
         <v>1</v>
@@ -6757,13 +6783,13 @@
         <v>1</v>
       </c>
       <c r="H59">
-        <v>0.6929729566508773</v>
+        <v>0.69297295665087733</v>
       </c>
       <c r="I59">
-        <v>0.9598677062968006</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9">
+        <v>0.95986770629680063</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>67</v>
       </c>
@@ -6777,7 +6803,7 @@
         <v>1104</v>
       </c>
       <c r="E60">
-        <v>0.9999999999666667</v>
+        <v>0.99999999996666666</v>
       </c>
       <c r="F60">
         <v>1</v>
@@ -6789,10 +6815,10 @@
         <v>0.7495348507597025</v>
       </c>
       <c r="I60">
-        <v>0.3315059224997621</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9">
+        <v>0.33150592249976207</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>68</v>
       </c>
@@ -6806,7 +6832,7 @@
         <v>1105</v>
       </c>
       <c r="E61">
-        <v>0.9999999999666667</v>
+        <v>0.99999999996666666</v>
       </c>
       <c r="F61">
         <v>1</v>
@@ -6815,13 +6841,13 @@
         <v>1</v>
       </c>
       <c r="H61">
-        <v>0.6821474615030683</v>
+        <v>0.68214746150306826</v>
       </c>
       <c r="I61">
-        <v>0.6190990642146503</v>
-      </c>
-    </row>
-    <row r="62" spans="1:9">
+        <v>0.61909906421465033</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>69</v>
       </c>
@@ -6835,22 +6861,22 @@
         <v>1106</v>
       </c>
       <c r="E62">
-        <v>0.9999999999666667</v>
+        <v>0.99999999996666666</v>
       </c>
       <c r="F62">
-        <v>0.8333333333333334</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="G62">
         <v>1</v>
       </c>
       <c r="H62">
-        <v>0.7295690104127214</v>
+        <v>0.72956901041272137</v>
       </c>
       <c r="I62">
-        <v>0.5773001661826465</v>
-      </c>
-    </row>
-    <row r="63" spans="1:9">
+        <v>0.57730016618264646</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>70</v>
       </c>
@@ -6864,7 +6890,7 @@
         <v>1107</v>
       </c>
       <c r="E63">
-        <v>0.9999999999666667</v>
+        <v>0.99999999996666666</v>
       </c>
       <c r="F63">
         <v>0</v>
@@ -6873,13 +6899,13 @@
         <v>0.25</v>
       </c>
       <c r="H63">
-        <v>0.703726422493975</v>
+        <v>0.70372642249397499</v>
       </c>
       <c r="I63">
-        <v>0.7867030347395654</v>
-      </c>
-    </row>
-    <row r="64" spans="1:9">
+        <v>0.78670303473956538</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>71</v>
       </c>
@@ -6893,7 +6919,7 @@
         <v>1108</v>
       </c>
       <c r="E64">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F64">
         <v>0</v>
@@ -6905,10 +6931,10 @@
         <v>0</v>
       </c>
       <c r="I64">
-        <v>0.4663627240577616</v>
-      </c>
-    </row>
-    <row r="65" spans="1:9">
+        <v>0.46636272405776158</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>72</v>
       </c>
@@ -6922,7 +6948,7 @@
         <v>1109</v>
       </c>
       <c r="E65">
-        <v>0.9999999999666667</v>
+        <v>0.99999999996666666</v>
       </c>
       <c r="F65">
         <v>1</v>
@@ -6931,13 +6957,13 @@
         <v>1</v>
       </c>
       <c r="H65">
-        <v>0.7092613470422459</v>
+        <v>0.70926134704224586</v>
       </c>
       <c r="I65">
-        <v>0.6488944080107782</v>
-      </c>
-    </row>
-    <row r="66" spans="1:9">
+        <v>0.64889440801077825</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>73</v>
       </c>
@@ -6960,13 +6986,13 @@
         <v>1</v>
       </c>
       <c r="H66">
-        <v>0.5424150950699871</v>
+        <v>0.54241509506998709</v>
       </c>
       <c r="I66">
-        <v>0.8198782028644943</v>
-      </c>
-    </row>
-    <row r="67" spans="1:9">
+        <v>0.81987820286449431</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>74</v>
       </c>
@@ -6980,22 +7006,22 @@
         <v>1111</v>
       </c>
       <c r="E67">
-        <v>0.9999999999666667</v>
+        <v>0.99999999996666666</v>
       </c>
       <c r="F67">
         <v>0.8</v>
       </c>
       <c r="G67">
-        <v>0.8333333333333334</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="H67">
         <v>0.4897506447265359</v>
       </c>
       <c r="I67">
-        <v>0.823843909514588</v>
-      </c>
-    </row>
-    <row r="68" spans="1:9">
+        <v>0.82384390951458797</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>75</v>
       </c>
@@ -7009,7 +7035,7 @@
         <v>1112</v>
       </c>
       <c r="E68">
-        <v>0.3333333333</v>
+        <v>0.33333333329999998</v>
       </c>
       <c r="F68">
         <v>0</v>
@@ -7018,13 +7044,13 @@
         <v>0.5</v>
       </c>
       <c r="H68">
-        <v>0.6244225389175652</v>
+        <v>0.62442253891756516</v>
       </c>
       <c r="I68">
-        <v>0.2035992348548598</v>
-      </c>
-    </row>
-    <row r="69" spans="1:9">
+        <v>0.20359923485485981</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>76</v>
       </c>
@@ -7038,7 +7064,7 @@
         <v>1113</v>
       </c>
       <c r="E69">
-        <v>0.9999999999666667</v>
+        <v>0.99999999996666666</v>
       </c>
       <c r="F69">
         <v>1</v>
@@ -7047,13 +7073,13 @@
         <v>1</v>
       </c>
       <c r="H69">
-        <v>0.5774589698347657</v>
+        <v>0.57745896983476575</v>
       </c>
       <c r="I69">
-        <v>0.462844647081411</v>
-      </c>
-    </row>
-    <row r="70" spans="1:9">
+        <v>0.46284464708141099</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>77</v>
       </c>
@@ -7067,22 +7093,22 @@
         <v>1114</v>
       </c>
       <c r="E70">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F70">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="G70">
         <v>0.5</v>
       </c>
       <c r="H70">
-        <v>0.5841534734892644</v>
+        <v>0.58415347348926439</v>
       </c>
       <c r="I70">
-        <v>0.6095152054999819</v>
-      </c>
-    </row>
-    <row r="71" spans="1:9">
+        <v>0.60951520549998195</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>78</v>
       </c>
@@ -7105,13 +7131,13 @@
         <v>1</v>
       </c>
       <c r="H71">
-        <v>0.5804837142508359</v>
+        <v>0.58048371425083589</v>
       </c>
       <c r="I71">
-        <v>0.4899674103830657</v>
-      </c>
-    </row>
-    <row r="72" spans="1:9">
+        <v>0.48996741038306568</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>79</v>
       </c>
@@ -7125,7 +7151,7 @@
         <v>1116</v>
       </c>
       <c r="E72">
-        <v>0.9999999999666667</v>
+        <v>0.99999999996666666</v>
       </c>
       <c r="F72">
         <v>1</v>
@@ -7134,13 +7160,13 @@
         <v>1</v>
       </c>
       <c r="H72">
-        <v>0.6645721027366219</v>
+        <v>0.66457210273662193</v>
       </c>
       <c r="I72">
-        <v>0.7854423596296523</v>
-      </c>
-    </row>
-    <row r="73" spans="1:9">
+        <v>0.78544235962965225</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>80</v>
       </c>
@@ -7154,7 +7180,7 @@
         <v>1117</v>
       </c>
       <c r="E73">
-        <v>0.5833333333041666</v>
+        <v>0.58333333330416659</v>
       </c>
       <c r="F73">
         <v>1</v>
@@ -7163,13 +7189,13 @@
         <v>1</v>
       </c>
       <c r="H73">
-        <v>0.4796195114001773</v>
+        <v>0.47961951140017728</v>
       </c>
       <c r="I73">
         <v>0.4228743803330467</v>
       </c>
     </row>
-    <row r="74" spans="1:9">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>81</v>
       </c>
@@ -7183,7 +7209,7 @@
         <v>1118</v>
       </c>
       <c r="E74">
-        <v>0.9999999999666667</v>
+        <v>0.99999999996666666</v>
       </c>
       <c r="F74">
         <v>0.6</v>
@@ -7195,10 +7221,10 @@
         <v>0.3337500135381945</v>
       </c>
       <c r="I74">
-        <v>0.3708659893619944</v>
-      </c>
-    </row>
-    <row r="75" spans="1:9">
+        <v>0.37086598936199439</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>82</v>
       </c>
@@ -7212,7 +7238,7 @@
         <v>1119</v>
       </c>
       <c r="E75">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F75">
         <v>1</v>
@@ -7221,13 +7247,13 @@
         <v>1</v>
       </c>
       <c r="H75">
-        <v>0.4495092884548446</v>
+        <v>0.44950928845484461</v>
       </c>
       <c r="I75">
-        <v>0.9569515668504643</v>
-      </c>
-    </row>
-    <row r="76" spans="1:9">
+        <v>0.95695156685046434</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>83</v>
       </c>
@@ -7241,7 +7267,7 @@
         <v>1120</v>
       </c>
       <c r="E76">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F76">
         <v>1</v>
@@ -7250,13 +7276,13 @@
         <v>1</v>
       </c>
       <c r="H76">
-        <v>0.469495496905991</v>
+        <v>0.46949549690599102</v>
       </c>
       <c r="I76">
-        <v>0.7233258602798205</v>
-      </c>
-    </row>
-    <row r="77" spans="1:9">
+        <v>0.72332586027982049</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>84</v>
       </c>
@@ -7270,7 +7296,7 @@
         <v>1121</v>
       </c>
       <c r="E77">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F77">
         <v>1</v>
@@ -7279,13 +7305,13 @@
         <v>1</v>
       </c>
       <c r="H77">
-        <v>0.5694178191147452</v>
+        <v>0.56941781911474521</v>
       </c>
       <c r="I77">
-        <v>0.6604529486152906</v>
-      </c>
-    </row>
-    <row r="78" spans="1:9">
+        <v>0.66045294861529058</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>85</v>
       </c>
@@ -7299,7 +7325,7 @@
         <v>1122</v>
       </c>
       <c r="E78">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F78">
         <v>1</v>
@@ -7311,10 +7337,10 @@
         <v>0.1546871488454965</v>
       </c>
       <c r="I78">
-        <v>0.6226864676684082</v>
-      </c>
-    </row>
-    <row r="79" spans="1:9">
+        <v>0.62268646766840818</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>86</v>
       </c>
@@ -7328,7 +7354,7 @@
         <v>1123</v>
       </c>
       <c r="E79">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F79">
         <v>1</v>
@@ -7337,13 +7363,13 @@
         <v>1</v>
       </c>
       <c r="H79">
-        <v>0.5112406868964985</v>
+        <v>0.51124068689649849</v>
       </c>
       <c r="I79">
-        <v>0.96750639101601</v>
-      </c>
-    </row>
-    <row r="80" spans="1:9">
+        <v>0.96750639101600999</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>87</v>
       </c>
@@ -7357,7 +7383,7 @@
         <v>1124</v>
       </c>
       <c r="E80">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F80">
         <v>1</v>
@@ -7366,13 +7392,13 @@
         <v>1</v>
       </c>
       <c r="H80">
-        <v>0.5653767463151658</v>
+        <v>0.56537674631516577</v>
       </c>
       <c r="I80">
-        <v>0.516980795597565</v>
-      </c>
-    </row>
-    <row r="81" spans="1:9">
+        <v>0.51698079559756505</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>88</v>
       </c>
@@ -7386,7 +7412,7 @@
         <v>1125</v>
       </c>
       <c r="E81">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F81">
         <v>1</v>
@@ -7395,13 +7421,13 @@
         <v>0.5</v>
       </c>
       <c r="H81">
-        <v>0.3960060675540709</v>
+        <v>0.39600606755407092</v>
       </c>
       <c r="I81">
         <v>0.7942645657968842</v>
       </c>
     </row>
-    <row r="82" spans="1:9">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>89</v>
       </c>
@@ -7424,13 +7450,13 @@
         <v>1</v>
       </c>
       <c r="H82">
-        <v>0.5111629053437182</v>
+        <v>0.51116290534371822</v>
       </c>
       <c r="I82">
-        <v>0.6034505111482449</v>
-      </c>
-    </row>
-    <row r="83" spans="1:9">
+        <v>0.60345051114824488</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>90</v>
       </c>
@@ -7453,13 +7479,13 @@
         <v>1</v>
       </c>
       <c r="H83">
-        <v>0.4228072589445787</v>
+        <v>0.42280725894457871</v>
       </c>
       <c r="I83">
-        <v>0.9550901393084963</v>
-      </c>
-    </row>
-    <row r="84" spans="1:9">
+        <v>0.95509013930849629</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>91</v>
       </c>
@@ -7473,22 +7499,22 @@
         <v>1128</v>
       </c>
       <c r="E84">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F84">
         <v>1</v>
       </c>
       <c r="G84">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="H84">
-        <v>0.4321595660563479</v>
+        <v>0.43215956605634792</v>
       </c>
       <c r="I84">
-        <v>0.6832276599915871</v>
-      </c>
-    </row>
-    <row r="85" spans="1:9">
+        <v>0.68322765999158708</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>92</v>
       </c>
@@ -7502,7 +7528,7 @@
         <v>1129</v>
       </c>
       <c r="E85">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F85">
         <v>1</v>
@@ -7511,13 +7537,13 @@
         <v>1</v>
       </c>
       <c r="H85">
-        <v>0.3766324972053364</v>
+        <v>0.37663249720533643</v>
       </c>
       <c r="I85">
-        <v>0.9393498823989235</v>
-      </c>
-    </row>
-    <row r="86" spans="1:9">
+        <v>0.93934988239892347</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>93</v>
       </c>
@@ -7540,13 +7566,13 @@
         <v>0.75</v>
       </c>
       <c r="H86">
-        <v>0.4484572418463498</v>
+        <v>0.44845724184634977</v>
       </c>
       <c r="I86">
-        <v>0.1209503413936179</v>
-      </c>
-    </row>
-    <row r="87" spans="1:9">
+        <v>0.12095034139361791</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>94</v>
       </c>
@@ -7560,22 +7586,22 @@
         <v>1131</v>
       </c>
       <c r="E87">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F87">
         <v>1</v>
       </c>
       <c r="G87">
-        <v>0.3333333333333333</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="H87">
-        <v>0.7551002131334609</v>
+        <v>0.75510021313346087</v>
       </c>
       <c r="I87">
-        <v>0.6687626720986138</v>
-      </c>
-    </row>
-    <row r="88" spans="1:9">
+        <v>0.66876267209861384</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>95</v>
       </c>
@@ -7589,7 +7615,7 @@
         <v>1132</v>
       </c>
       <c r="E88">
-        <v>0.8333333332916666</v>
+        <v>0.83333333329166659</v>
       </c>
       <c r="F88">
         <v>1</v>
@@ -7598,13 +7624,13 @@
         <v>1</v>
       </c>
       <c r="H88">
-        <v>0.7802586206799685</v>
+        <v>0.78025862067996854</v>
       </c>
       <c r="I88">
-        <v>0.838429510791078</v>
-      </c>
-    </row>
-    <row r="89" spans="1:9">
+        <v>0.83842951079107797</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>96</v>
       </c>
@@ -7627,13 +7653,13 @@
         <v>0.8</v>
       </c>
       <c r="H89">
-        <v>0.6843411735196172</v>
+        <v>0.68434117351961721</v>
       </c>
       <c r="I89">
-        <v>0.1892267116571097</v>
-      </c>
-    </row>
-    <row r="90" spans="1:9">
+        <v>0.18922671165710969</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>97</v>
       </c>
@@ -7656,13 +7682,13 @@
         <v>0</v>
       </c>
       <c r="H90">
-        <v>0.5030083504700322</v>
+        <v>0.50300835047003223</v>
       </c>
       <c r="I90">
-        <v>0.1753503563590144</v>
-      </c>
-    </row>
-    <row r="91" spans="1:9">
+        <v>0.17535035635901439</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>98</v>
       </c>
@@ -7676,7 +7702,7 @@
         <v>1135</v>
       </c>
       <c r="E91">
-        <v>0.9999999999666667</v>
+        <v>0.99999999996666666</v>
       </c>
       <c r="F91">
         <v>0.75</v>
@@ -7685,13 +7711,13 @@
         <v>1</v>
       </c>
       <c r="H91">
-        <v>0.558718900493589</v>
+        <v>0.55871890049358897</v>
       </c>
       <c r="I91">
-        <v>0.5006699483593086</v>
-      </c>
-    </row>
-    <row r="92" spans="1:9">
+        <v>0.50066994835930856</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>99</v>
       </c>
@@ -7714,13 +7740,13 @@
         <v>0</v>
       </c>
       <c r="H92">
-        <v>0.6154062259413656</v>
+        <v>0.61540622594136563</v>
       </c>
       <c r="I92">
         <v>0.1756669196290313</v>
       </c>
     </row>
-    <row r="93" spans="1:9">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>100</v>
       </c>
@@ -7734,7 +7760,7 @@
         <v>1137</v>
       </c>
       <c r="E93">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F93">
         <v>1</v>
@@ -7743,13 +7769,13 @@
         <v>1</v>
       </c>
       <c r="H93">
-        <v>0.7465151034164937</v>
+        <v>0.74651510341649374</v>
       </c>
       <c r="I93">
-        <v>0.9160718792134426</v>
-      </c>
-    </row>
-    <row r="94" spans="1:9">
+        <v>0.91607187921344257</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>101</v>
       </c>
@@ -7769,16 +7795,16 @@
         <v>1</v>
       </c>
       <c r="G94">
-        <v>0.3636363636363636</v>
+        <v>0.36363636363636359</v>
       </c>
       <c r="H94">
-        <v>0.5744443894635898</v>
+        <v>0.57444438946358978</v>
       </c>
       <c r="I94">
-        <v>0.4241632352049531</v>
-      </c>
-    </row>
-    <row r="95" spans="1:9">
+        <v>0.42416323520495308</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>102</v>
       </c>
@@ -7792,22 +7818,22 @@
         <v>1139</v>
       </c>
       <c r="E95">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F95">
         <v>1</v>
       </c>
       <c r="G95">
-        <v>0.8333333333333334</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="H95">
-        <v>0.6561318223898313</v>
+        <v>0.65613182238983125</v>
       </c>
       <c r="I95">
-        <v>0.4826093934799636</v>
-      </c>
-    </row>
-    <row r="96" spans="1:9">
+        <v>0.48260939347996362</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>103</v>
       </c>
@@ -7833,10 +7859,10 @@
         <v>0.5416840146111902</v>
       </c>
       <c r="I96">
-        <v>0.7924535557448965</v>
-      </c>
-    </row>
-    <row r="97" spans="1:9">
+        <v>0.79245355574489651</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>104</v>
       </c>
@@ -7856,16 +7882,16 @@
         <v>1</v>
       </c>
       <c r="G97">
-        <v>0.8333333333333334</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="H97">
-        <v>0.5861419339098716</v>
+        <v>0.58614193390987157</v>
       </c>
       <c r="I97">
         <v>0.6741549532920299</v>
       </c>
     </row>
-    <row r="98" spans="1:9">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>105</v>
       </c>
@@ -7879,7 +7905,7 @@
         <v>1142</v>
       </c>
       <c r="E98">
-        <v>0.9999999999666667</v>
+        <v>0.99999999996666666</v>
       </c>
       <c r="F98">
         <v>1</v>
@@ -7888,13 +7914,13 @@
         <v>1</v>
       </c>
       <c r="H98">
-        <v>0.5006534190970393</v>
+        <v>0.50065341909703931</v>
       </c>
       <c r="I98">
-        <v>0.9741648637915081</v>
-      </c>
-    </row>
-    <row r="99" spans="1:9">
+        <v>0.97416486379150813</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>106</v>
       </c>
@@ -7908,7 +7934,7 @@
         <v>1143</v>
       </c>
       <c r="E99">
-        <v>0.9999999999666667</v>
+        <v>0.99999999996666666</v>
       </c>
       <c r="F99">
         <v>1</v>
@@ -7917,13 +7943,13 @@
         <v>1</v>
       </c>
       <c r="H99">
-        <v>0.525861660125004</v>
+        <v>0.52586166012500402</v>
       </c>
       <c r="I99">
-        <v>0.2597045113548122</v>
-      </c>
-    </row>
-    <row r="100" spans="1:9">
+        <v>0.25970451135481221</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>107</v>
       </c>
@@ -7937,7 +7963,7 @@
         <v>1144</v>
       </c>
       <c r="E100">
-        <v>0.9999999999666667</v>
+        <v>0.99999999996666666</v>
       </c>
       <c r="F100">
         <v>1</v>
@@ -7946,13 +7972,13 @@
         <v>1</v>
       </c>
       <c r="H100">
-        <v>0.5528650488361765</v>
+        <v>0.55286504883617649</v>
       </c>
       <c r="I100">
-        <v>0.6557101427416399</v>
-      </c>
-    </row>
-    <row r="101" spans="1:9">
+        <v>0.65571014274163986</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>108</v>
       </c>
@@ -7966,7 +7992,7 @@
         <v>1145</v>
       </c>
       <c r="E101">
-        <v>0.9999999999666667</v>
+        <v>0.99999999996666666</v>
       </c>
       <c r="F101">
         <v>1</v>
@@ -7975,13 +8001,13 @@
         <v>1</v>
       </c>
       <c r="H101">
-        <v>0.600450038770417</v>
+        <v>0.60045003877041703</v>
       </c>
       <c r="I101">
-        <v>0.5991953110089001</v>
-      </c>
-    </row>
-    <row r="102" spans="1:9">
+        <v>0.59919531100890011</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>109</v>
       </c>
@@ -7995,7 +8021,7 @@
         <v>1146</v>
       </c>
       <c r="E102">
-        <v>0.5833333333041666</v>
+        <v>0.58333333330416659</v>
       </c>
       <c r="F102">
         <v>1</v>
@@ -8004,13 +8030,13 @@
         <v>1</v>
       </c>
       <c r="H102">
-        <v>0.4684892773081519</v>
+        <v>0.46848927730815187</v>
       </c>
       <c r="I102">
-        <v>0.9563847862110351</v>
-      </c>
-    </row>
-    <row r="103" spans="1:9">
+        <v>0.95638478621103507</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>110</v>
       </c>
@@ -8024,7 +8050,7 @@
         <v>1147</v>
       </c>
       <c r="E103">
-        <v>0.9999999999666667</v>
+        <v>0.99999999996666666</v>
       </c>
       <c r="F103">
         <v>1</v>
@@ -8033,13 +8059,13 @@
         <v>1</v>
       </c>
       <c r="H103">
-        <v>0.5633061274423417</v>
+        <v>0.56330612744234165</v>
       </c>
       <c r="I103">
-        <v>0.4300158153905307</v>
-      </c>
-    </row>
-    <row r="104" spans="1:9">
+        <v>0.43001581539053069</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>111</v>
       </c>
@@ -8053,7 +8079,7 @@
         <v>1148</v>
       </c>
       <c r="E104">
-        <v>0.3333333333</v>
+        <v>0.33333333329999998</v>
       </c>
       <c r="F104">
         <v>1</v>
@@ -8062,13 +8088,13 @@
         <v>1</v>
       </c>
       <c r="H104">
-        <v>0.4556060234367387</v>
+        <v>0.45560602343673873</v>
       </c>
       <c r="I104">
-        <v>0.9363575323217572</v>
-      </c>
-    </row>
-    <row r="105" spans="1:9">
+        <v>0.93635753232175722</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>112</v>
       </c>
@@ -8082,7 +8108,7 @@
         <v>1149</v>
       </c>
       <c r="E105">
-        <v>0.9999999999666667</v>
+        <v>0.99999999996666666</v>
       </c>
       <c r="F105">
         <v>1</v>
@@ -8091,13 +8117,13 @@
         <v>1</v>
       </c>
       <c r="H105">
-        <v>0.5453645753935666</v>
+        <v>0.54536457539356664</v>
       </c>
       <c r="I105">
-        <v>0.806838047045923</v>
-      </c>
-    </row>
-    <row r="106" spans="1:9">
+        <v>0.80683804704592299</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>113</v>
       </c>
@@ -8120,13 +8146,13 @@
         <v>1</v>
       </c>
       <c r="H106">
-        <v>0.5624648708242216</v>
+        <v>0.56246487082422159</v>
       </c>
       <c r="I106">
         <v>0.156551559416653</v>
       </c>
     </row>
-    <row r="107" spans="1:9">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>114</v>
       </c>
@@ -8140,7 +8166,7 @@
         <v>1151</v>
       </c>
       <c r="E107">
-        <v>0.9999999999666667</v>
+        <v>0.99999999996666666</v>
       </c>
       <c r="F107">
         <v>1</v>
@@ -8149,13 +8175,13 @@
         <v>1</v>
       </c>
       <c r="H107">
-        <v>0.7694696261453479</v>
+        <v>0.76946962614534786</v>
       </c>
       <c r="I107">
-        <v>0.4996376677780351</v>
-      </c>
-    </row>
-    <row r="108" spans="1:9">
+        <v>0.49963766777803509</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>115</v>
       </c>
@@ -8169,7 +8195,7 @@
         <v>1152</v>
       </c>
       <c r="E108">
-        <v>0.9999999999666667</v>
+        <v>0.99999999996666666</v>
       </c>
       <c r="F108">
         <v>1</v>
@@ -8178,13 +8204,13 @@
         <v>1</v>
       </c>
       <c r="H108">
-        <v>0.6622135443705288</v>
+        <v>0.66221354437052882</v>
       </c>
       <c r="I108">
-        <v>0.7991738441713925</v>
-      </c>
-    </row>
-    <row r="109" spans="1:9">
+        <v>0.79917384417139248</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>116</v>
       </c>
@@ -8207,13 +8233,13 @@
         <v>0.75</v>
       </c>
       <c r="H109">
-        <v>0.7897894210312582</v>
+        <v>0.78978942103125815</v>
       </c>
       <c r="I109">
-        <v>0.349479878575348</v>
-      </c>
-    </row>
-    <row r="110" spans="1:9">
+        <v>0.34947987857534801</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>117</v>
       </c>
@@ -8236,13 +8262,13 @@
         <v>1</v>
       </c>
       <c r="H110">
-        <v>0.427180192478621</v>
+        <v>0.42718019247862099</v>
       </c>
       <c r="I110">
-        <v>0.7915645050635743</v>
-      </c>
-    </row>
-    <row r="111" spans="1:9">
+        <v>0.79156450506357434</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>118</v>
       </c>
@@ -8256,7 +8282,7 @@
         <v>1155</v>
       </c>
       <c r="E111">
-        <v>0.9999999999666667</v>
+        <v>0.99999999996666666</v>
       </c>
       <c r="F111">
         <v>1</v>
@@ -8268,10 +8294,10 @@
         <v>0.5993430172636921</v>
       </c>
       <c r="I111">
-        <v>0.6774591192234889</v>
-      </c>
-    </row>
-    <row r="112" spans="1:9">
+        <v>0.67745911922348889</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>119</v>
       </c>
@@ -8294,13 +8320,13 @@
         <v>1</v>
       </c>
       <c r="H112">
-        <v>0.5351693161834387</v>
+        <v>0.53516931618343866</v>
       </c>
       <c r="I112">
-        <v>0.8812190898206815</v>
-      </c>
-    </row>
-    <row r="113" spans="1:9">
+        <v>0.88121908982068153</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>120</v>
       </c>
@@ -8323,13 +8349,13 @@
         <v>1</v>
       </c>
       <c r="H113">
-        <v>0.6999636113302308</v>
+        <v>0.69996361133023077</v>
       </c>
       <c r="I113">
-        <v>0.9304908395349836</v>
-      </c>
-    </row>
-    <row r="114" spans="1:9">
+        <v>0.93049083953498357</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>121</v>
       </c>
@@ -8343,7 +8369,7 @@
         <v>1158</v>
       </c>
       <c r="E114">
-        <v>0.9999999999666667</v>
+        <v>0.99999999996666666</v>
       </c>
       <c r="F114">
         <v>1</v>
@@ -8355,10 +8381,10 @@
         <v>0.5591586054020995</v>
       </c>
       <c r="I114">
-        <v>0.5897184359959822</v>
-      </c>
-    </row>
-    <row r="115" spans="1:9">
+        <v>0.58971843599598217</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>122</v>
       </c>
@@ -8372,7 +8398,7 @@
         <v>1159</v>
       </c>
       <c r="E115">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F115">
         <v>1</v>
@@ -8381,13 +8407,13 @@
         <v>1</v>
       </c>
       <c r="H115">
-        <v>0.8964800751246519</v>
+        <v>0.89648007512465189</v>
       </c>
       <c r="I115">
-        <v>0.9169960359004248</v>
-      </c>
-    </row>
-    <row r="116" spans="1:9">
+        <v>0.91699603590042478</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>123</v>
       </c>
@@ -8401,7 +8427,7 @@
         <v>1160</v>
       </c>
       <c r="E116">
-        <v>0.8333333332916666</v>
+        <v>0.83333333329166659</v>
       </c>
       <c r="F116">
         <v>1</v>
@@ -8410,10 +8436,10 @@
         <v>1</v>
       </c>
       <c r="H116">
-        <v>0.500357502492539</v>
-      </c>
-    </row>
-    <row r="117" spans="1:9">
+        <v>0.50035750249253896</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>124</v>
       </c>
@@ -8436,13 +8462,13 @@
         <v>0</v>
       </c>
       <c r="H117">
-        <v>0.5994670841662705</v>
+        <v>0.59946708416627048</v>
       </c>
       <c r="I117">
-        <v>0.1507162280792081</v>
-      </c>
-    </row>
-    <row r="118" spans="1:9">
+        <v>0.15071622807920809</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>125</v>
       </c>
@@ -8456,7 +8482,7 @@
         <v>1162</v>
       </c>
       <c r="E118">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F118">
         <v>1</v>
@@ -8465,13 +8491,13 @@
         <v>1</v>
       </c>
       <c r="H118">
-        <v>0.2977777172851057</v>
+        <v>0.29777771728510571</v>
       </c>
       <c r="I118">
-        <v>0.6773223990389001</v>
-      </c>
-    </row>
-    <row r="119" spans="1:9">
+        <v>0.67732239903890012</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>126</v>
       </c>
@@ -8494,13 +8520,13 @@
         <v>0</v>
       </c>
       <c r="H119">
-        <v>0.3867850724992615</v>
+        <v>0.38678507249926147</v>
       </c>
       <c r="I119">
         <v>0.12944197325987</v>
       </c>
     </row>
-    <row r="120" spans="1:9">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>127</v>
       </c>
@@ -8514,7 +8540,7 @@
         <v>1164</v>
       </c>
       <c r="E120">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F120">
         <v>1</v>
@@ -8523,13 +8549,13 @@
         <v>1</v>
       </c>
       <c r="H120">
-        <v>0.4584577333923746</v>
+        <v>0.45845773339237461</v>
       </c>
       <c r="I120">
-        <v>0.958450406732005</v>
-      </c>
-    </row>
-    <row r="121" spans="1:9">
+        <v>0.95845040673200499</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>128</v>
       </c>
@@ -8543,7 +8569,7 @@
         <v>1165</v>
       </c>
       <c r="E121">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F121">
         <v>1</v>
@@ -8552,13 +8578,13 @@
         <v>1</v>
       </c>
       <c r="H121">
-        <v>0.6089218326653479</v>
+        <v>0.60892183266534794</v>
       </c>
       <c r="I121">
-        <v>0.5315193295679901</v>
-      </c>
-    </row>
-    <row r="122" spans="1:9">
+        <v>0.53151932956799008</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>129</v>
       </c>
@@ -8572,7 +8598,7 @@
         <v>1166</v>
       </c>
       <c r="E122">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F122">
         <v>1</v>
@@ -8581,13 +8607,13 @@
         <v>1</v>
       </c>
       <c r="H122">
-        <v>0.4279210247087802</v>
+        <v>0.42792102470878018</v>
       </c>
       <c r="I122">
-        <v>0.4105371526352143</v>
-      </c>
-    </row>
-    <row r="123" spans="1:9">
+        <v>0.41053715263521429</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>130</v>
       </c>
@@ -8601,7 +8627,7 @@
         <v>1167</v>
       </c>
       <c r="E123">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F123">
         <v>1</v>
@@ -8610,13 +8636,13 @@
         <v>1</v>
       </c>
       <c r="H123">
-        <v>0.5314162205536562</v>
+        <v>0.53141622055365623</v>
       </c>
       <c r="I123">
-        <v>0.5756202565480824</v>
-      </c>
-    </row>
-    <row r="124" spans="1:9">
+        <v>0.57562025654808235</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>131</v>
       </c>
@@ -8642,10 +8668,10 @@
         <v>0</v>
       </c>
       <c r="I124">
-        <v>0.4558734376106879</v>
-      </c>
-    </row>
-    <row r="125" spans="1:9">
+        <v>0.45587343761068788</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>132</v>
       </c>
@@ -8659,7 +8685,7 @@
         <v>1169</v>
       </c>
       <c r="E125">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F125">
         <v>1</v>
@@ -8671,10 +8697,10 @@
         <v>0.4290987826033244</v>
       </c>
       <c r="I125">
-        <v>0.3247682993948298</v>
-      </c>
-    </row>
-    <row r="126" spans="1:9">
+        <v>0.32476829939482982</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>133</v>
       </c>
@@ -8688,7 +8714,7 @@
         <v>1170</v>
       </c>
       <c r="E126">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F126">
         <v>1</v>
@@ -8697,13 +8723,13 @@
         <v>1</v>
       </c>
       <c r="H126">
-        <v>0.4680066020138537</v>
+        <v>0.46800660201385369</v>
       </c>
       <c r="I126">
-        <v>0.4739600381726777</v>
-      </c>
-    </row>
-    <row r="127" spans="1:9">
+        <v>0.47396003817267768</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>134</v>
       </c>
@@ -8717,22 +8743,22 @@
         <v>1171</v>
       </c>
       <c r="E127">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F127">
         <v>1</v>
       </c>
       <c r="G127">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="H127">
-        <v>0.4920694636470362</v>
+        <v>0.49206946364703619</v>
       </c>
       <c r="I127">
-        <v>0.8425322417545962</v>
-      </c>
-    </row>
-    <row r="128" spans="1:9">
+        <v>0.84253224175459618</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>135</v>
       </c>
@@ -8755,13 +8781,13 @@
         <v>1</v>
       </c>
       <c r="H128">
-        <v>0.4810455512966981</v>
+        <v>0.48104555129669813</v>
       </c>
       <c r="I128">
-        <v>0.4689571411318734</v>
-      </c>
-    </row>
-    <row r="129" spans="1:9">
+        <v>0.46895714113187342</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>136</v>
       </c>
@@ -8784,13 +8810,13 @@
         <v>1</v>
       </c>
       <c r="H129">
-        <v>0.4047677747271536</v>
+        <v>0.40476777472715358</v>
       </c>
       <c r="I129">
         <v>0.5641976477697318</v>
       </c>
     </row>
-    <row r="130" spans="1:9">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>137</v>
       </c>
@@ -8804,7 +8830,7 @@
         <v>819</v>
       </c>
       <c r="E130">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F130">
         <v>1</v>
@@ -8813,13 +8839,13 @@
         <v>1</v>
       </c>
       <c r="H130">
-        <v>0.3236983751537894</v>
+        <v>0.32369837515378941</v>
       </c>
       <c r="I130">
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:9">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>138</v>
       </c>
@@ -8833,7 +8859,7 @@
         <v>1174</v>
       </c>
       <c r="E131">
-        <v>0.9999999999666667</v>
+        <v>0.99999999996666666</v>
       </c>
       <c r="F131">
         <v>1</v>
@@ -8842,13 +8868,13 @@
         <v>0.75</v>
       </c>
       <c r="H131">
-        <v>0.5295681127327955</v>
+        <v>0.52956811273279547</v>
       </c>
       <c r="I131">
-        <v>0.9726795147378249</v>
-      </c>
-    </row>
-    <row r="132" spans="1:9">
+        <v>0.97267951473782488</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>139</v>
       </c>
@@ -8862,7 +8888,7 @@
         <v>1175</v>
       </c>
       <c r="E132">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F132">
         <v>1</v>
@@ -8871,13 +8897,13 @@
         <v>1</v>
       </c>
       <c r="H132">
-        <v>0.3451847427769206</v>
+        <v>0.34518474277692057</v>
       </c>
       <c r="I132">
         <v>0.9514596986739523</v>
       </c>
     </row>
-    <row r="133" spans="1:9">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>140</v>
       </c>
@@ -8900,13 +8926,13 @@
         <v>1</v>
       </c>
       <c r="H133">
-        <v>0.2770228732962366</v>
+        <v>0.27702287329623659</v>
       </c>
       <c r="I133">
-        <v>0.7338286614665011</v>
-      </c>
-    </row>
-    <row r="134" spans="1:9">
+        <v>0.73382866146650105</v>
+      </c>
+    </row>
+    <row r="134" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>141</v>
       </c>
@@ -8920,7 +8946,7 @@
         <v>1177</v>
       </c>
       <c r="E134">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F134">
         <v>1</v>
@@ -8929,13 +8955,13 @@
         <v>1</v>
       </c>
       <c r="H134">
-        <v>0.3212217461822087</v>
+        <v>0.32122174618220872</v>
       </c>
       <c r="I134">
         <v>0.9876214381313474</v>
       </c>
     </row>
-    <row r="135" spans="1:9">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>142</v>
       </c>
@@ -8949,7 +8975,7 @@
         <v>1178</v>
       </c>
       <c r="E135">
-        <v>0.8333333332916666</v>
+        <v>0.83333333329166659</v>
       </c>
       <c r="F135">
         <v>1</v>
@@ -8958,13 +8984,13 @@
         <v>1</v>
       </c>
       <c r="H135">
-        <v>0.437673039849804</v>
+        <v>0.43767303984980399</v>
       </c>
       <c r="I135">
-        <v>0.9504192285462802</v>
-      </c>
-    </row>
-    <row r="136" spans="1:9">
+        <v>0.95041922854628025</v>
+      </c>
+    </row>
+    <row r="136" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>143</v>
       </c>
@@ -8978,7 +9004,7 @@
         <v>1179</v>
       </c>
       <c r="E136">
-        <v>0.9999999999666667</v>
+        <v>0.99999999996666666</v>
       </c>
       <c r="F136">
         <v>1</v>
@@ -8987,13 +9013,13 @@
         <v>1</v>
       </c>
       <c r="H136">
-        <v>0.6178978353477717</v>
+        <v>0.61789783534777165</v>
       </c>
       <c r="I136">
         <v>0.9887845302050271</v>
       </c>
     </row>
-    <row r="137" spans="1:9">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>144</v>
       </c>
@@ -9007,7 +9033,7 @@
         <v>1180</v>
       </c>
       <c r="E137">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F137">
         <v>1</v>
@@ -9016,13 +9042,13 @@
         <v>1</v>
       </c>
       <c r="H137">
-        <v>0.3269337050418469</v>
+        <v>0.32693370504184688</v>
       </c>
       <c r="I137">
-        <v>0.6710522528948555</v>
-      </c>
-    </row>
-    <row r="138" spans="1:9">
+        <v>0.67105225289485548</v>
+      </c>
+    </row>
+    <row r="138" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>145</v>
       </c>
@@ -9042,16 +9068,16 @@
         <v>1</v>
       </c>
       <c r="G138">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="H138">
-        <v>0.410819489816265</v>
+        <v>0.41081948981626498</v>
       </c>
       <c r="I138">
-        <v>0.4230717011790864</v>
-      </c>
-    </row>
-    <row r="139" spans="1:9">
+        <v>0.42307170117908638</v>
+      </c>
+    </row>
+    <row r="139" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>146</v>
       </c>
@@ -9074,13 +9100,13 @@
         <v>1</v>
       </c>
       <c r="H139">
-        <v>0.4268304532770175</v>
+        <v>0.42683045327701752</v>
       </c>
       <c r="I139">
-        <v>0.5873408590306832</v>
-      </c>
-    </row>
-    <row r="140" spans="1:9">
+        <v>0.58734085903068323</v>
+      </c>
+    </row>
+    <row r="140" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>147</v>
       </c>
@@ -9094,7 +9120,7 @@
         <v>1183</v>
       </c>
       <c r="E140">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F140">
         <v>0</v>
@@ -9103,13 +9129,13 @@
         <v>0.7142857142857143</v>
       </c>
       <c r="H140">
-        <v>0.5563195964740978</v>
+        <v>0.55631959647409779</v>
       </c>
       <c r="I140">
-        <v>0.1595567185740059</v>
-      </c>
-    </row>
-    <row r="141" spans="1:9">
+        <v>0.15955671857400591</v>
+      </c>
+    </row>
+    <row r="141" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>148</v>
       </c>
@@ -9123,7 +9149,7 @@
         <v>1184</v>
       </c>
       <c r="E141">
-        <v>0.9999999999666667</v>
+        <v>0.99999999996666666</v>
       </c>
       <c r="F141">
         <v>1</v>
@@ -9132,13 +9158,13 @@
         <v>1</v>
       </c>
       <c r="H141">
-        <v>0.7330528642672091</v>
+        <v>0.73305286426720906</v>
       </c>
       <c r="I141">
         <v>0.9574696544909036</v>
       </c>
     </row>
-    <row r="142" spans="1:9">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>149</v>
       </c>
@@ -9152,7 +9178,7 @@
         <v>1185</v>
       </c>
       <c r="E142">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F142">
         <v>1</v>
@@ -9161,13 +9187,13 @@
         <v>1</v>
       </c>
       <c r="H142">
-        <v>0.6131938950520288</v>
+        <v>0.61319389505202881</v>
       </c>
       <c r="I142">
-        <v>0.7404790447874193</v>
-      </c>
-    </row>
-    <row r="143" spans="1:9">
+        <v>0.74047904478741933</v>
+      </c>
+    </row>
+    <row r="143" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>150</v>
       </c>
@@ -9181,7 +9207,7 @@
         <v>1186</v>
       </c>
       <c r="E143">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F143">
         <v>1</v>
@@ -9190,13 +9216,13 @@
         <v>1</v>
       </c>
       <c r="H143">
-        <v>0.462705121262095</v>
+        <v>0.46270512126209501</v>
       </c>
       <c r="I143">
-        <v>0.7225663944637286</v>
-      </c>
-    </row>
-    <row r="144" spans="1:9">
+        <v>0.72256639446372861</v>
+      </c>
+    </row>
+    <row r="144" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>151</v>
       </c>
@@ -9210,7 +9236,7 @@
         <v>1187</v>
       </c>
       <c r="E144">
-        <v>0.8333333332916666</v>
+        <v>0.83333333329166659</v>
       </c>
       <c r="F144">
         <v>1</v>
@@ -9219,13 +9245,13 @@
         <v>0</v>
       </c>
       <c r="H144">
-        <v>0.890019909327759</v>
+        <v>0.89001990932775898</v>
       </c>
       <c r="I144">
-        <v>0.9465784554245296</v>
-      </c>
-    </row>
-    <row r="145" spans="1:9">
+        <v>0.94657845542452956</v>
+      </c>
+    </row>
+    <row r="145" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>152</v>
       </c>
@@ -9248,13 +9274,13 @@
         <v>0.8</v>
       </c>
       <c r="H145">
-        <v>0.530287957068527</v>
+        <v>0.53028795706852705</v>
       </c>
       <c r="I145">
-        <v>0.6265070852617787</v>
-      </c>
-    </row>
-    <row r="146" spans="1:9">
+        <v>0.62650708526177867</v>
+      </c>
+    </row>
+    <row r="146" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>153</v>
       </c>
@@ -9268,7 +9294,7 @@
         <v>1189</v>
       </c>
       <c r="E146">
-        <v>0.8333333332916666</v>
+        <v>0.83333333329166659</v>
       </c>
       <c r="F146">
         <v>1</v>
@@ -9277,13 +9303,13 @@
         <v>1</v>
       </c>
       <c r="H146">
-        <v>0.5246586983446072</v>
+        <v>0.52465869834460721</v>
       </c>
       <c r="I146">
-        <v>0.9680075360414939</v>
-      </c>
-    </row>
-    <row r="147" spans="1:9">
+        <v>0.96800753604149392</v>
+      </c>
+    </row>
+    <row r="147" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>154</v>
       </c>
@@ -9309,10 +9335,10 @@
         <v>0.6538022903123003</v>
       </c>
       <c r="I147">
-        <v>0.9066431850439374</v>
-      </c>
-    </row>
-    <row r="148" spans="1:9">
+        <v>0.90664318504393737</v>
+      </c>
+    </row>
+    <row r="148" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>155</v>
       </c>
@@ -9326,7 +9352,7 @@
         <v>1191</v>
       </c>
       <c r="E148">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F148">
         <v>1</v>
@@ -9335,10 +9361,10 @@
         <v>1</v>
       </c>
       <c r="H148">
-        <v>0.6193602897563706</v>
-      </c>
-    </row>
-    <row r="149" spans="1:9">
+        <v>0.61936028975637059</v>
+      </c>
+    </row>
+    <row r="149" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>156</v>
       </c>
@@ -9352,7 +9378,7 @@
         <v>1192</v>
       </c>
       <c r="E149">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F149">
         <v>1</v>
@@ -9364,10 +9390,10 @@
         <v>0.2562560023220164</v>
       </c>
       <c r="I149">
-        <v>0.5391846498639341</v>
-      </c>
-    </row>
-    <row r="150" spans="1:9">
+        <v>0.53918464986393411</v>
+      </c>
+    </row>
+    <row r="150" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>157</v>
       </c>
@@ -9381,7 +9407,7 @@
         <v>1193</v>
       </c>
       <c r="E150">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F150">
         <v>1</v>
@@ -9390,13 +9416,13 @@
         <v>1</v>
       </c>
       <c r="H150">
-        <v>0.477032859727483</v>
+        <v>0.47703285972748299</v>
       </c>
       <c r="I150">
-        <v>0.9614960583856575</v>
-      </c>
-    </row>
-    <row r="151" spans="1:9">
+        <v>0.96149605838565755</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>158</v>
       </c>
@@ -9410,7 +9436,7 @@
         <v>1194</v>
       </c>
       <c r="E151">
-        <v>0.8333333332916666</v>
+        <v>0.83333333329166659</v>
       </c>
       <c r="F151">
         <v>1</v>
@@ -9419,13 +9445,13 @@
         <v>1</v>
       </c>
       <c r="H151">
-        <v>0.6451152548013872</v>
+        <v>0.64511525480138721</v>
       </c>
       <c r="I151">
-        <v>0.9749640664159702</v>
-      </c>
-    </row>
-    <row r="152" spans="1:9">
+        <v>0.97496406641597022</v>
+      </c>
+    </row>
+    <row r="152" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>159</v>
       </c>
@@ -9439,7 +9465,7 @@
         <v>1195</v>
       </c>
       <c r="E152">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F152">
         <v>1</v>
@@ -9448,13 +9474,13 @@
         <v>1</v>
       </c>
       <c r="H152">
-        <v>0.5929175574009301</v>
+        <v>0.59291755740093011</v>
       </c>
       <c r="I152">
-        <v>0.4623230109434553</v>
-      </c>
-    </row>
-    <row r="153" spans="1:9">
+        <v>0.46232301094345529</v>
+      </c>
+    </row>
+    <row r="153" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>160</v>
       </c>
@@ -9468,7 +9494,7 @@
         <v>1196</v>
       </c>
       <c r="E153">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F153">
         <v>1</v>
@@ -9477,13 +9503,13 @@
         <v>1</v>
       </c>
       <c r="H153">
-        <v>0.2869627494331357</v>
+        <v>0.28696274943313571</v>
       </c>
       <c r="I153">
-        <v>0.7805107516269861</v>
-      </c>
-    </row>
-    <row r="154" spans="1:9">
+        <v>0.78051075162698613</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>161</v>
       </c>
@@ -9497,7 +9523,7 @@
         <v>1197</v>
       </c>
       <c r="E154">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F154">
         <v>1</v>
@@ -9506,13 +9532,13 @@
         <v>1</v>
       </c>
       <c r="H154">
-        <v>0.4613147242693048</v>
+        <v>0.46131472426930481</v>
       </c>
       <c r="I154">
-        <v>0.5194487783045503</v>
-      </c>
-    </row>
-    <row r="155" spans="1:9">
+        <v>0.51944877830455027</v>
+      </c>
+    </row>
+    <row r="155" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>162</v>
       </c>
@@ -9526,7 +9552,7 @@
         <v>1198</v>
       </c>
       <c r="E155">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F155">
         <v>1</v>
@@ -9535,13 +9561,13 @@
         <v>1</v>
       </c>
       <c r="H155">
-        <v>0.3789146860197043</v>
+        <v>0.37891468601970429</v>
       </c>
       <c r="I155">
-        <v>0.6973291017704881</v>
-      </c>
-    </row>
-    <row r="156" spans="1:9">
+        <v>0.69732910177048812</v>
+      </c>
+    </row>
+    <row r="156" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>163</v>
       </c>
@@ -9564,13 +9590,13 @@
         <v>1</v>
       </c>
       <c r="H156">
-        <v>0.2504672359730971</v>
+        <v>0.25046723597309711</v>
       </c>
       <c r="I156">
-        <v>0.182496998381413</v>
-      </c>
-    </row>
-    <row r="157" spans="1:9">
+        <v>0.18249699838141301</v>
+      </c>
+    </row>
+    <row r="157" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>164</v>
       </c>
@@ -9593,13 +9619,13 @@
         <v>0</v>
       </c>
       <c r="H157">
-        <v>0.6669890451442552</v>
+        <v>0.66698904514425517</v>
       </c>
       <c r="I157">
-        <v>0.7596619453078841</v>
-      </c>
-    </row>
-    <row r="158" spans="1:9">
+        <v>0.75966194530788411</v>
+      </c>
+    </row>
+    <row r="158" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>165</v>
       </c>
@@ -9622,13 +9648,13 @@
         <v>0.5</v>
       </c>
       <c r="H158">
-        <v>0.6029830434727357</v>
+        <v>0.60298304347273568</v>
       </c>
       <c r="I158">
-        <v>0.6023061769880387</v>
-      </c>
-    </row>
-    <row r="159" spans="1:9">
+        <v>0.60230617698803868</v>
+      </c>
+    </row>
+    <row r="159" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>166</v>
       </c>
@@ -9642,7 +9668,7 @@
         <v>1202</v>
       </c>
       <c r="E159">
-        <v>0.9999999999666667</v>
+        <v>0.99999999996666666</v>
       </c>
       <c r="F159">
         <v>1</v>
@@ -9654,10 +9680,10 @@
         <v>0.3348543815575265</v>
       </c>
       <c r="I159">
-        <v>0.7020870490354914</v>
-      </c>
-    </row>
-    <row r="160" spans="1:9">
+        <v>0.70208704903549135</v>
+      </c>
+    </row>
+    <row r="160" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>167</v>
       </c>
@@ -9680,13 +9706,13 @@
         <v>1</v>
       </c>
       <c r="H160">
-        <v>0.450538830371418</v>
+        <v>0.45053883037141801</v>
       </c>
       <c r="I160">
         <v>0.6944271037093237</v>
       </c>
     </row>
-    <row r="161" spans="1:9">
+    <row r="161" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>168</v>
       </c>
@@ -9700,7 +9726,7 @@
         <v>1204</v>
       </c>
       <c r="E161">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F161">
         <v>1</v>
@@ -9709,13 +9735,13 @@
         <v>1</v>
       </c>
       <c r="H161">
-        <v>0.3971389619561354</v>
+        <v>0.39713896195613541</v>
       </c>
       <c r="I161">
-        <v>0.6863592097351424</v>
-      </c>
-    </row>
-    <row r="162" spans="1:9">
+        <v>0.68635920973514242</v>
+      </c>
+    </row>
+    <row r="162" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>169</v>
       </c>
@@ -9729,7 +9755,7 @@
         <v>1205</v>
       </c>
       <c r="E162">
-        <v>0.9999999999666667</v>
+        <v>0.99999999996666666</v>
       </c>
       <c r="F162">
         <v>1</v>
@@ -9738,13 +9764,13 @@
         <v>1</v>
       </c>
       <c r="H162">
-        <v>0.5106617782560858</v>
+        <v>0.51066177825608583</v>
       </c>
       <c r="I162">
         <v>0.7915389169666267</v>
       </c>
     </row>
-    <row r="163" spans="1:9">
+    <row r="163" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>170</v>
       </c>
@@ -9767,13 +9793,13 @@
         <v>1</v>
       </c>
       <c r="H163">
-        <v>0.4854252997970471</v>
+        <v>0.48542529979704713</v>
       </c>
       <c r="I163">
-        <v>0.8781478551626904</v>
-      </c>
-    </row>
-    <row r="164" spans="1:9">
+        <v>0.87814785516269045</v>
+      </c>
+    </row>
+    <row r="164" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>171</v>
       </c>
@@ -9787,7 +9813,7 @@
         <v>1207</v>
       </c>
       <c r="E164">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F164">
         <v>1</v>
@@ -9796,13 +9822,13 @@
         <v>1</v>
       </c>
       <c r="H164">
-        <v>0.6163063629044137</v>
+        <v>0.61630636290441365</v>
       </c>
       <c r="I164">
-        <v>0.9864015929695251</v>
-      </c>
-    </row>
-    <row r="165" spans="1:9">
+        <v>0.98640159296952512</v>
+      </c>
+    </row>
+    <row r="165" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>172</v>
       </c>
@@ -9825,13 +9851,13 @@
         <v>1</v>
       </c>
       <c r="H165">
-        <v>0.3965454516375088</v>
+        <v>0.39654545163750882</v>
       </c>
       <c r="I165">
-        <v>0.7024333074351869</v>
-      </c>
-    </row>
-    <row r="166" spans="1:9">
+        <v>0.70243330743518695</v>
+      </c>
+    </row>
+    <row r="166" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>173</v>
       </c>
@@ -9845,7 +9871,7 @@
         <v>1209</v>
       </c>
       <c r="E166">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F166">
         <v>1</v>
@@ -9860,7 +9886,7 @@
         <v>0.9281092398437113</v>
       </c>
     </row>
-    <row r="167" spans="1:9">
+    <row r="167" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>174</v>
       </c>
@@ -9874,7 +9900,7 @@
         <v>1210</v>
       </c>
       <c r="E167">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F167">
         <v>1</v>
@@ -9883,13 +9909,13 @@
         <v>1</v>
       </c>
       <c r="H167">
-        <v>0.3325902321061615</v>
+        <v>0.33259023210616151</v>
       </c>
       <c r="I167">
-        <v>0.5856121478199474</v>
-      </c>
-    </row>
-    <row r="168" spans="1:9">
+        <v>0.58561214781994742</v>
+      </c>
+    </row>
+    <row r="168" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>175</v>
       </c>
@@ -9903,7 +9929,7 @@
         <v>1211</v>
       </c>
       <c r="E168">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F168">
         <v>1</v>
@@ -9912,13 +9938,13 @@
         <v>1</v>
       </c>
       <c r="H168">
-        <v>0.5211564020352653</v>
+        <v>0.52115640203526525</v>
       </c>
       <c r="I168">
-        <v>0.4733208420455393</v>
-      </c>
-    </row>
-    <row r="169" spans="1:9">
+        <v>0.47332084204553931</v>
+      </c>
+    </row>
+    <row r="169" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>176</v>
       </c>
@@ -9932,7 +9958,7 @@
         <v>1212</v>
       </c>
       <c r="E169">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F169">
         <v>1</v>
@@ -9944,10 +9970,10 @@
         <v>0.3719521130820701</v>
       </c>
       <c r="I169">
-        <v>0.6306529362021496</v>
-      </c>
-    </row>
-    <row r="170" spans="1:9">
+        <v>0.63065293620214957</v>
+      </c>
+    </row>
+    <row r="170" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>177</v>
       </c>
@@ -9961,7 +9987,7 @@
         <v>1213</v>
       </c>
       <c r="E170">
-        <v>0.9999999999666667</v>
+        <v>0.99999999996666666</v>
       </c>
       <c r="F170">
         <v>0</v>
@@ -9970,13 +9996,13 @@
         <v>0.8571428571428571</v>
       </c>
       <c r="H170">
-        <v>0.6044742152954795</v>
+        <v>0.60447421529547951</v>
       </c>
       <c r="I170">
         <v>0.5890406002534786</v>
       </c>
     </row>
-    <row r="171" spans="1:9">
+    <row r="171" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>178</v>
       </c>
@@ -9990,7 +10016,7 @@
         <v>1214</v>
       </c>
       <c r="E171">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F171">
         <v>1</v>
@@ -9999,13 +10025,13 @@
         <v>1</v>
       </c>
       <c r="H171">
-        <v>0.4250463538631998</v>
+        <v>0.42504635386319978</v>
       </c>
       <c r="I171">
-        <v>0.8136683835382711</v>
-      </c>
-    </row>
-    <row r="172" spans="1:9">
+        <v>0.81366838353827109</v>
+      </c>
+    </row>
+    <row r="172" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>179</v>
       </c>
@@ -10019,7 +10045,7 @@
         <v>1215</v>
       </c>
       <c r="E172">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F172">
         <v>1</v>
@@ -10028,13 +10054,13 @@
         <v>1</v>
       </c>
       <c r="H172">
-        <v>0.2158659357589383</v>
+        <v>0.21586593575893831</v>
       </c>
       <c r="I172">
-        <v>0.9697818535209656</v>
-      </c>
-    </row>
-    <row r="173" spans="1:9">
+        <v>0.96978185352096558</v>
+      </c>
+    </row>
+    <row r="173" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>180</v>
       </c>
@@ -10048,7 +10074,7 @@
         <v>1216</v>
       </c>
       <c r="E173">
-        <v>0.9999999999666667</v>
+        <v>0.99999999996666666</v>
       </c>
       <c r="F173">
         <v>1</v>
@@ -10057,13 +10083,13 @@
         <v>1</v>
       </c>
       <c r="H173">
-        <v>0.5621193990163598</v>
+        <v>0.56211939901635977</v>
       </c>
       <c r="I173">
-        <v>0.9120606235434905</v>
-      </c>
-    </row>
-    <row r="174" spans="1:9">
+        <v>0.91206062354349049</v>
+      </c>
+    </row>
+    <row r="174" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>181</v>
       </c>
@@ -10086,13 +10112,13 @@
         <v>1</v>
       </c>
       <c r="H174">
-        <v>0.6042081299124443</v>
+        <v>0.60420812991244432</v>
       </c>
       <c r="I174">
-        <v>0.5899966812800314</v>
-      </c>
-    </row>
-    <row r="175" spans="1:9">
+        <v>0.58999668128003135</v>
+      </c>
+    </row>
+    <row r="175" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>182</v>
       </c>
@@ -10106,7 +10132,7 @@
         <v>1218</v>
       </c>
       <c r="E175">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F175">
         <v>1</v>
@@ -10115,13 +10141,13 @@
         <v>1</v>
       </c>
       <c r="H175">
-        <v>0.5035401951102517</v>
+        <v>0.50354019511025172</v>
       </c>
       <c r="I175">
         <v>0.6153890422761632</v>
       </c>
     </row>
-    <row r="176" spans="1:9">
+    <row r="176" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>183</v>
       </c>
@@ -10144,13 +10170,13 @@
         <v>1</v>
       </c>
       <c r="H176">
-        <v>0.5210984783059219</v>
+        <v>0.52109847830592193</v>
       </c>
       <c r="I176">
-        <v>0.6046014959180148</v>
-      </c>
-    </row>
-    <row r="177" spans="1:9">
+        <v>0.60460149591801482</v>
+      </c>
+    </row>
+    <row r="177" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>184</v>
       </c>
@@ -10164,7 +10190,7 @@
         <v>1220</v>
       </c>
       <c r="E177">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F177">
         <v>1</v>
@@ -10173,13 +10199,13 @@
         <v>1</v>
       </c>
       <c r="H177">
-        <v>0.4074121032850495</v>
+        <v>0.40741210328504951</v>
       </c>
       <c r="I177">
-        <v>0.9972545691521211</v>
-      </c>
-    </row>
-    <row r="178" spans="1:9">
+        <v>0.99725456915212107</v>
+      </c>
+    </row>
+    <row r="178" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>185</v>
       </c>
@@ -10193,7 +10219,7 @@
         <v>1221</v>
       </c>
       <c r="E178">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F178">
         <v>1</v>
@@ -10205,10 +10231,10 @@
         <v>0.6011105267187592</v>
       </c>
       <c r="I178">
-        <v>0.9443265315418793</v>
-      </c>
-    </row>
-    <row r="179" spans="1:9">
+        <v>0.94432653154187929</v>
+      </c>
+    </row>
+    <row r="179" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>186</v>
       </c>
@@ -10222,7 +10248,7 @@
         <v>1222</v>
       </c>
       <c r="E179">
-        <v>0.8333333332916666</v>
+        <v>0.83333333329166659</v>
       </c>
       <c r="F179">
         <v>1</v>
@@ -10234,10 +10260,10 @@
         <v>0.6843824076634748</v>
       </c>
       <c r="I179">
-        <v>0.810619814605257</v>
-      </c>
-    </row>
-    <row r="180" spans="1:9">
+        <v>0.81061981460525701</v>
+      </c>
+    </row>
+    <row r="180" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>187</v>
       </c>
@@ -10251,7 +10277,7 @@
         <v>1223</v>
       </c>
       <c r="E180">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F180">
         <v>1</v>
@@ -10260,13 +10286,13 @@
         <v>1</v>
       </c>
       <c r="H180">
-        <v>0.4685669464944902</v>
+        <v>0.46856694649449021</v>
       </c>
       <c r="I180">
-        <v>0.9956842544250601</v>
-      </c>
-    </row>
-    <row r="181" spans="1:9">
+        <v>0.99568425442506014</v>
+      </c>
+    </row>
+    <row r="181" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>188</v>
       </c>
@@ -10280,7 +10306,7 @@
         <v>1224</v>
       </c>
       <c r="E181">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F181">
         <v>1</v>
@@ -10289,13 +10315,13 @@
         <v>1</v>
       </c>
       <c r="H181">
-        <v>0.3727971472324454</v>
+        <v>0.37279714723244539</v>
       </c>
       <c r="I181">
-        <v>0.517127734980063</v>
-      </c>
-    </row>
-    <row r="182" spans="1:9">
+        <v>0.51712773498006304</v>
+      </c>
+    </row>
+    <row r="182" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>189</v>
       </c>
@@ -10309,7 +10335,7 @@
         <v>1225</v>
       </c>
       <c r="E182">
-        <v>0.8333333332916666</v>
+        <v>0.83333333329166659</v>
       </c>
       <c r="F182">
         <v>1</v>
@@ -10321,10 +10347,10 @@
         <v>0.4457332788436788</v>
       </c>
       <c r="I182">
-        <v>0.82933475077788</v>
-      </c>
-    </row>
-    <row r="183" spans="1:9">
+        <v>0.82933475077787999</v>
+      </c>
+    </row>
+    <row r="183" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>190</v>
       </c>
@@ -10338,7 +10364,7 @@
         <v>1226</v>
       </c>
       <c r="E183">
-        <v>0.8333333332916666</v>
+        <v>0.83333333329166659</v>
       </c>
       <c r="F183">
         <v>1</v>
@@ -10347,13 +10373,13 @@
         <v>1</v>
       </c>
       <c r="H183">
-        <v>0.766025379064348</v>
+        <v>0.76602537906434798</v>
       </c>
       <c r="I183">
-        <v>0.647719011049634</v>
-      </c>
-    </row>
-    <row r="184" spans="1:9">
+        <v>0.64771901104963403</v>
+      </c>
+    </row>
+    <row r="184" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>191</v>
       </c>
@@ -10367,7 +10393,7 @@
         <v>1227</v>
       </c>
       <c r="E184">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F184">
         <v>1</v>
@@ -10376,13 +10402,13 @@
         <v>1</v>
       </c>
       <c r="H184">
-        <v>0.5482244183887908</v>
+        <v>0.54822441838879077</v>
       </c>
       <c r="I184">
-        <v>0.5191540337903656</v>
-      </c>
-    </row>
-    <row r="185" spans="1:9">
+        <v>0.51915403379036562</v>
+      </c>
+    </row>
+    <row r="185" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>192</v>
       </c>
@@ -10396,7 +10422,7 @@
         <v>1228</v>
       </c>
       <c r="E185">
-        <v>0.9999999999666667</v>
+        <v>0.99999999996666666</v>
       </c>
       <c r="F185">
         <v>1</v>
@@ -10405,13 +10431,13 @@
         <v>0.75</v>
       </c>
       <c r="H185">
-        <v>0.3475325574811159</v>
+        <v>0.34753255748111589</v>
       </c>
       <c r="I185">
         <v>0.7639251674477634</v>
       </c>
     </row>
-    <row r="186" spans="1:9">
+    <row r="186" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>193</v>
       </c>
@@ -10425,7 +10451,7 @@
         <v>1229</v>
       </c>
       <c r="E186">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F186">
         <v>1</v>
@@ -10434,13 +10460,13 @@
         <v>0.8</v>
       </c>
       <c r="H186">
-        <v>0.5108626829933903</v>
+        <v>0.51086268299339033</v>
       </c>
       <c r="I186">
-        <v>0.5596251090981417</v>
-      </c>
-    </row>
-    <row r="187" spans="1:9">
+        <v>0.55962510909814167</v>
+      </c>
+    </row>
+    <row r="187" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>194</v>
       </c>
@@ -10463,13 +10489,13 @@
         <v>0</v>
       </c>
       <c r="H187">
-        <v>0.3389483826613048</v>
+        <v>0.33894838266130478</v>
       </c>
       <c r="I187">
-        <v>0.7079909464143876</v>
-      </c>
-    </row>
-    <row r="188" spans="1:9">
+        <v>0.70799094641438765</v>
+      </c>
+    </row>
+    <row r="188" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>195</v>
       </c>
@@ -10483,7 +10509,7 @@
         <v>1231</v>
       </c>
       <c r="E188">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F188">
         <v>1</v>
@@ -10492,13 +10518,13 @@
         <v>1</v>
       </c>
       <c r="H188">
-        <v>0.5360804609220974</v>
+        <v>0.53608046092209738</v>
       </c>
       <c r="I188">
-        <v>0.7191196407614108</v>
-      </c>
-    </row>
-    <row r="189" spans="1:9">
+        <v>0.71911964076141077</v>
+      </c>
+    </row>
+    <row r="189" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>196</v>
       </c>
@@ -10512,7 +10538,7 @@
         <v>1232</v>
       </c>
       <c r="E189">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F189">
         <v>1</v>
@@ -10521,10 +10547,10 @@
         <v>1</v>
       </c>
       <c r="H189">
-        <v>0.5472421108265464</v>
-      </c>
-    </row>
-    <row r="190" spans="1:9">
+        <v>0.54724211082654639</v>
+      </c>
+    </row>
+    <row r="190" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>197</v>
       </c>
@@ -10538,7 +10564,7 @@
         <v>1233</v>
       </c>
       <c r="E190">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F190">
         <v>1</v>
@@ -10547,13 +10573,13 @@
         <v>1</v>
       </c>
       <c r="H190">
-        <v>0.4474689667075459</v>
+        <v>0.44746896670754588</v>
       </c>
       <c r="I190">
-        <v>0.9967382135716404</v>
-      </c>
-    </row>
-    <row r="191" spans="1:9">
+        <v>0.99673821357164039</v>
+      </c>
+    </row>
+    <row r="191" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>198</v>
       </c>
@@ -10567,7 +10593,7 @@
         <v>1234</v>
       </c>
       <c r="E191">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F191">
         <v>1</v>
@@ -10576,13 +10602,13 @@
         <v>1</v>
       </c>
       <c r="H191">
-        <v>0.641200566199878</v>
+        <v>0.64120056619987797</v>
       </c>
       <c r="I191">
-        <v>0.6629626464429592</v>
-      </c>
-    </row>
-    <row r="192" spans="1:9">
+        <v>0.66296264644295921</v>
+      </c>
+    </row>
+    <row r="192" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>199</v>
       </c>
@@ -10596,7 +10622,7 @@
         <v>1235</v>
       </c>
       <c r="E192">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F192">
         <v>1</v>
@@ -10608,10 +10634,10 @@
         <v>0</v>
       </c>
       <c r="I192">
-        <v>0.8016496388647458</v>
-      </c>
-    </row>
-    <row r="193" spans="1:9">
+        <v>0.80164963886474583</v>
+      </c>
+    </row>
+    <row r="193" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>200</v>
       </c>
@@ -10625,7 +10651,7 @@
         <v>1236</v>
       </c>
       <c r="E193">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F193">
         <v>1</v>
@@ -10634,13 +10660,13 @@
         <v>0.6</v>
       </c>
       <c r="H193">
-        <v>0.5651883935530639</v>
+        <v>0.56518839355306394</v>
       </c>
       <c r="I193">
-        <v>0.5214575464303138</v>
-      </c>
-    </row>
-    <row r="194" spans="1:9">
+        <v>0.52145754643031383</v>
+      </c>
+    </row>
+    <row r="194" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>201</v>
       </c>
@@ -10654,7 +10680,7 @@
         <v>1237</v>
       </c>
       <c r="E194">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F194">
         <v>1</v>
@@ -10663,13 +10689,13 @@
         <v>1</v>
       </c>
       <c r="H194">
-        <v>0.3537928620903577</v>
+        <v>0.35379286209035771</v>
       </c>
       <c r="I194">
-        <v>0.5856003445824204</v>
-      </c>
-    </row>
-    <row r="195" spans="1:9">
+        <v>0.58560034458242038</v>
+      </c>
+    </row>
+    <row r="195" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>202</v>
       </c>
@@ -10683,7 +10709,7 @@
         <v>1238</v>
       </c>
       <c r="E195">
-        <v>0.8333333332916666</v>
+        <v>0.83333333329166659</v>
       </c>
       <c r="F195">
         <v>1</v>
@@ -10692,13 +10718,13 @@
         <v>1</v>
       </c>
       <c r="H195">
-        <v>0.7877858350073553</v>
+        <v>0.78778583500735533</v>
       </c>
       <c r="I195">
-        <v>0.7802494758730673</v>
-      </c>
-    </row>
-    <row r="196" spans="1:9">
+        <v>0.78024947587306726</v>
+      </c>
+    </row>
+    <row r="196" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>203</v>
       </c>
@@ -10721,13 +10747,13 @@
         <v>0.75</v>
       </c>
       <c r="H196">
-        <v>0.6578029052884695</v>
+        <v>0.65780290528846952</v>
       </c>
       <c r="I196">
-        <v>0.6716727713140695</v>
-      </c>
-    </row>
-    <row r="197" spans="1:9">
+        <v>0.67167277131406955</v>
+      </c>
+    </row>
+    <row r="197" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>204</v>
       </c>
@@ -10750,13 +10776,13 @@
         <v>1</v>
       </c>
       <c r="H197">
-        <v>0.7796403738109277</v>
+        <v>0.77964037381092766</v>
       </c>
       <c r="I197">
         <v>0.1320889625501078</v>
       </c>
     </row>
-    <row r="198" spans="1:9">
+    <row r="198" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>205</v>
       </c>
@@ -10770,7 +10796,7 @@
         <v>1241</v>
       </c>
       <c r="E198">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F198">
         <v>1</v>
@@ -10779,13 +10805,13 @@
         <v>1</v>
       </c>
       <c r="H198">
-        <v>0.4134402304274972</v>
+        <v>0.41344023042749722</v>
       </c>
       <c r="I198">
-        <v>0.4957143379759665</v>
-      </c>
-    </row>
-    <row r="199" spans="1:9">
+        <v>0.49571433797596648</v>
+      </c>
+    </row>
+    <row r="199" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>206</v>
       </c>
@@ -10799,7 +10825,7 @@
         <v>1242</v>
       </c>
       <c r="E199">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F199">
         <v>1</v>
@@ -10811,10 +10837,10 @@
         <v>0.5208101302971464</v>
       </c>
       <c r="I199">
-        <v>0.4258152752203446</v>
-      </c>
-    </row>
-    <row r="200" spans="1:9">
+        <v>0.42581527522034462</v>
+      </c>
+    </row>
+    <row r="200" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>207</v>
       </c>
@@ -10828,7 +10854,7 @@
         <v>1243</v>
       </c>
       <c r="E200">
-        <v>0.9999999999666667</v>
+        <v>0.99999999996666666</v>
       </c>
       <c r="F200">
         <v>1</v>
@@ -10840,10 +10866,10 @@
         <v>0</v>
       </c>
       <c r="I200">
-        <v>0.4739866957117834</v>
-      </c>
-    </row>
-    <row r="201" spans="1:9">
+        <v>0.47398669571178342</v>
+      </c>
+    </row>
+    <row r="201" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>208</v>
       </c>
@@ -10857,7 +10883,7 @@
         <v>1244</v>
       </c>
       <c r="E201">
-        <v>0.9999999999666667</v>
+        <v>0.99999999996666666</v>
       </c>
       <c r="F201">
         <v>1</v>
@@ -10866,13 +10892,13 @@
         <v>1</v>
       </c>
       <c r="H201">
-        <v>0.5739649838080136</v>
+        <v>0.57396498380801364</v>
       </c>
       <c r="I201">
-        <v>0.8163894165687375</v>
-      </c>
-    </row>
-    <row r="202" spans="1:9">
+        <v>0.81638941656873754</v>
+      </c>
+    </row>
+    <row r="202" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>209</v>
       </c>
@@ -10886,7 +10912,7 @@
         <v>1245</v>
       </c>
       <c r="E202">
-        <v>0.8333333332916666</v>
+        <v>0.83333333329166659</v>
       </c>
       <c r="F202">
         <v>1</v>
@@ -10895,13 +10921,13 @@
         <v>1</v>
       </c>
       <c r="H202">
-        <v>0.5531217071299593</v>
+        <v>0.55312170712995934</v>
       </c>
       <c r="I202">
-        <v>0.4939328159160374</v>
-      </c>
-    </row>
-    <row r="203" spans="1:9">
+        <v>0.49393281591603738</v>
+      </c>
+    </row>
+    <row r="203" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>210</v>
       </c>
@@ -10915,7 +10941,7 @@
         <v>1246</v>
       </c>
       <c r="E203">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F203">
         <v>1</v>
@@ -10927,10 +10953,10 @@
         <v>0.1323471072567183</v>
       </c>
       <c r="I203">
-        <v>0.4191553997323373</v>
-      </c>
-    </row>
-    <row r="204" spans="1:9">
+        <v>0.41915539973233729</v>
+      </c>
+    </row>
+    <row r="204" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>211</v>
       </c>
@@ -10944,7 +10970,7 @@
         <v>1247</v>
       </c>
       <c r="E204">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F204">
         <v>1</v>
@@ -10953,13 +10979,13 @@
         <v>1</v>
       </c>
       <c r="H204">
-        <v>0.6218962527350075</v>
+        <v>0.62189625273500748</v>
       </c>
       <c r="I204">
-        <v>0.4956895027410028</v>
-      </c>
-    </row>
-    <row r="205" spans="1:9">
+        <v>0.49568950274100282</v>
+      </c>
+    </row>
+    <row r="205" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>212</v>
       </c>
@@ -10973,7 +10999,7 @@
         <v>1248</v>
       </c>
       <c r="E205">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F205">
         <v>1</v>
@@ -10982,13 +11008,13 @@
         <v>1</v>
       </c>
       <c r="H205">
-        <v>0.407711878039098</v>
+        <v>0.40771187803909797</v>
       </c>
       <c r="I205">
-        <v>0.9701169668758158</v>
-      </c>
-    </row>
-    <row r="206" spans="1:9">
+        <v>0.97011696687581583</v>
+      </c>
+    </row>
+    <row r="206" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>213</v>
       </c>
@@ -11011,13 +11037,13 @@
         <v>1</v>
       </c>
       <c r="H206">
-        <v>0.6850711710186516</v>
+        <v>0.68507117101865156</v>
       </c>
       <c r="I206">
         <v>0.9841569389335515</v>
       </c>
     </row>
-    <row r="207" spans="1:9">
+    <row r="207" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>214</v>
       </c>
@@ -11031,7 +11057,7 @@
         <v>1250</v>
       </c>
       <c r="E207">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F207">
         <v>1</v>
@@ -11040,13 +11066,13 @@
         <v>1</v>
       </c>
       <c r="H207">
-        <v>0.6418725483997952</v>
+        <v>0.64187254839979524</v>
       </c>
       <c r="I207">
-        <v>0.9355123886734111</v>
-      </c>
-    </row>
-    <row r="208" spans="1:9">
+        <v>0.93551238867341113</v>
+      </c>
+    </row>
+    <row r="208" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>215</v>
       </c>
@@ -11060,7 +11086,7 @@
         <v>1251</v>
       </c>
       <c r="E208">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F208">
         <v>1</v>
@@ -11069,13 +11095,13 @@
         <v>1</v>
       </c>
       <c r="H208">
-        <v>0.5829783703975969</v>
+        <v>0.58297837039759692</v>
       </c>
       <c r="I208">
-        <v>0.9905217056279602</v>
-      </c>
-    </row>
-    <row r="209" spans="1:9">
+        <v>0.99052170562796016</v>
+      </c>
+    </row>
+    <row r="209" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>216</v>
       </c>
@@ -11098,13 +11124,13 @@
         <v>1</v>
       </c>
       <c r="H209">
-        <v>0.5554875908549908</v>
+        <v>0.55548759085499078</v>
       </c>
       <c r="I209">
         <v>0.4406798497390893</v>
       </c>
     </row>
-    <row r="210" spans="1:9">
+    <row r="210" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>217</v>
       </c>
@@ -11118,7 +11144,7 @@
         <v>1253</v>
       </c>
       <c r="E210">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F210">
         <v>1</v>
@@ -11127,13 +11153,13 @@
         <v>1</v>
       </c>
       <c r="H210">
-        <v>0.4474207178851686</v>
+        <v>0.44742071788516857</v>
       </c>
       <c r="I210">
-        <v>0.9989835417534995</v>
-      </c>
-    </row>
-    <row r="211" spans="1:9">
+        <v>0.99898354175349946</v>
+      </c>
+    </row>
+    <row r="211" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>218</v>
       </c>
@@ -11147,7 +11173,7 @@
         <v>1254</v>
       </c>
       <c r="E211">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F211">
         <v>1</v>
@@ -11159,10 +11185,10 @@
         <v>0.5815164382566369</v>
       </c>
       <c r="I211">
-        <v>0.6044312472552604</v>
-      </c>
-    </row>
-    <row r="212" spans="1:9">
+        <v>0.60443124725526043</v>
+      </c>
+    </row>
+    <row r="212" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>219</v>
       </c>
@@ -11176,7 +11202,7 @@
         <v>1255</v>
       </c>
       <c r="E212">
-        <v>0.9999999999666667</v>
+        <v>0.99999999996666666</v>
       </c>
       <c r="F212">
         <v>1</v>
@@ -11185,13 +11211,13 @@
         <v>1</v>
       </c>
       <c r="H212">
-        <v>0.7460685202098968</v>
+        <v>0.74606852020989678</v>
       </c>
       <c r="I212">
-        <v>0.9749317361675016</v>
-      </c>
-    </row>
-    <row r="213" spans="1:9">
+        <v>0.97493173616750162</v>
+      </c>
+    </row>
+    <row r="213" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>220</v>
       </c>
@@ -11205,7 +11231,7 @@
         <v>1256</v>
       </c>
       <c r="E213">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F213">
         <v>1</v>
@@ -11214,13 +11240,13 @@
         <v>1</v>
       </c>
       <c r="H213">
-        <v>0.4081135405278051</v>
+        <v>0.40811354052780507</v>
       </c>
       <c r="I213">
-        <v>0.9913999061616428</v>
-      </c>
-    </row>
-    <row r="214" spans="1:9">
+        <v>0.99139990616164275</v>
+      </c>
+    </row>
+    <row r="214" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>221</v>
       </c>
@@ -11243,13 +11269,13 @@
         <v>1</v>
       </c>
       <c r="H214">
-        <v>0.3524286746731459</v>
+        <v>0.35242867467314593</v>
       </c>
       <c r="I214">
-        <v>0.5272588114806014</v>
-      </c>
-    </row>
-    <row r="215" spans="1:9">
+        <v>0.52725881148060139</v>
+      </c>
+    </row>
+    <row r="215" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>222</v>
       </c>
@@ -11263,7 +11289,7 @@
         <v>1258</v>
       </c>
       <c r="E215">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F215">
         <v>1</v>
@@ -11272,13 +11298,13 @@
         <v>1</v>
       </c>
       <c r="H215">
-        <v>0.5185521872648697</v>
+        <v>0.51855218726486974</v>
       </c>
       <c r="I215">
-        <v>0.2221118264763358</v>
-      </c>
-    </row>
-    <row r="216" spans="1:9">
+        <v>0.22211182647633579</v>
+      </c>
+    </row>
+    <row r="216" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>223</v>
       </c>
@@ -11292,7 +11318,7 @@
         <v>1259</v>
       </c>
       <c r="E216">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F216">
         <v>1</v>
@@ -11301,13 +11327,13 @@
         <v>1</v>
       </c>
       <c r="H216">
-        <v>0.6389591451883503</v>
+        <v>0.63895914518835029</v>
       </c>
       <c r="I216">
-        <v>0.7903622950494245</v>
-      </c>
-    </row>
-    <row r="217" spans="1:9">
+        <v>0.79036229504942446</v>
+      </c>
+    </row>
+    <row r="217" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>224</v>
       </c>
@@ -11321,7 +11347,7 @@
         <v>1260</v>
       </c>
       <c r="E217">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F217">
         <v>1</v>
@@ -11330,13 +11356,13 @@
         <v>1</v>
       </c>
       <c r="H217">
-        <v>0.6973943608383181</v>
+        <v>0.69739436083831807</v>
       </c>
       <c r="I217">
-        <v>0.9930982012869041</v>
-      </c>
-    </row>
-    <row r="218" spans="1:9">
+        <v>0.99309820128690407</v>
+      </c>
+    </row>
+    <row r="218" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>225</v>
       </c>
@@ -11350,7 +11376,7 @@
         <v>907</v>
       </c>
       <c r="E218">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F218">
         <v>1</v>
@@ -11359,13 +11385,13 @@
         <v>1</v>
       </c>
       <c r="H218">
-        <v>0.3026395077138581</v>
+        <v>0.30263950771385811</v>
       </c>
       <c r="I218">
         <v>1</v>
       </c>
     </row>
-    <row r="219" spans="1:9">
+    <row r="219" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>226</v>
       </c>
@@ -11388,13 +11414,13 @@
         <v>1</v>
       </c>
       <c r="H219">
-        <v>0.3130911442582595</v>
+        <v>0.31309114425825951</v>
       </c>
       <c r="I219">
-        <v>0.7231269680803927</v>
-      </c>
-    </row>
-    <row r="220" spans="1:9">
+        <v>0.72312696808039267</v>
+      </c>
+    </row>
+    <row r="220" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>227</v>
       </c>
@@ -11408,22 +11434,22 @@
         <v>1262</v>
       </c>
       <c r="E220">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F220">
         <v>1</v>
       </c>
       <c r="G220">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="H220">
         <v>0.6537154531417545</v>
       </c>
       <c r="I220">
-        <v>0.8156749839007031</v>
-      </c>
-    </row>
-    <row r="221" spans="1:9">
+        <v>0.81567498390070314</v>
+      </c>
+    </row>
+    <row r="221" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>228</v>
       </c>
@@ -11437,7 +11463,7 @@
         <v>1263</v>
       </c>
       <c r="E221">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F221">
         <v>1</v>
@@ -11446,13 +11472,13 @@
         <v>1</v>
       </c>
       <c r="H221">
-        <v>0.6113234685347346</v>
+        <v>0.61132346853473463</v>
       </c>
       <c r="I221">
-        <v>0.5634879146857119</v>
-      </c>
-    </row>
-    <row r="222" spans="1:9">
+        <v>0.56348791468571191</v>
+      </c>
+    </row>
+    <row r="222" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>229</v>
       </c>
@@ -11472,16 +11498,16 @@
         <v>1</v>
       </c>
       <c r="G222">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="H222">
         <v>0.3946146077527255</v>
       </c>
       <c r="I222">
-        <v>0.9714242589461324</v>
-      </c>
-    </row>
-    <row r="223" spans="1:9">
+        <v>0.97142425894613238</v>
+      </c>
+    </row>
+    <row r="223" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>230</v>
       </c>
@@ -11495,7 +11521,7 @@
         <v>1265</v>
       </c>
       <c r="E223">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F223">
         <v>1</v>
@@ -11504,13 +11530,13 @@
         <v>0.875</v>
       </c>
       <c r="H223">
-        <v>0.3841011889459279</v>
+        <v>0.38410118894592787</v>
       </c>
       <c r="I223">
-        <v>0.708801695833454</v>
-      </c>
-    </row>
-    <row r="224" spans="1:9">
+        <v>0.70880169583345398</v>
+      </c>
+    </row>
+    <row r="224" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>231</v>
       </c>
@@ -11524,7 +11550,7 @@
         <v>1266</v>
       </c>
       <c r="E224">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F224">
         <v>1</v>
@@ -11533,13 +11559,13 @@
         <v>1</v>
       </c>
       <c r="H224">
-        <v>0.5517801452012858</v>
+        <v>0.55178014520128582</v>
       </c>
       <c r="I224">
-        <v>0.7556309276479649</v>
-      </c>
-    </row>
-    <row r="225" spans="1:9">
+        <v>0.75563092764796491</v>
+      </c>
+    </row>
+    <row r="225" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>232</v>
       </c>
@@ -11565,10 +11591,10 @@
         <v>0.3896419531999154</v>
       </c>
       <c r="I225">
-        <v>0.9488266637233277</v>
-      </c>
-    </row>
-    <row r="226" spans="1:9">
+        <v>0.94882666372332769</v>
+      </c>
+    </row>
+    <row r="226" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>233</v>
       </c>
@@ -11582,7 +11608,7 @@
         <v>1268</v>
       </c>
       <c r="E226">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F226">
         <v>1</v>
@@ -11591,13 +11617,13 @@
         <v>0.8</v>
       </c>
       <c r="H226">
-        <v>0.5906001196236351</v>
+        <v>0.59060011962363512</v>
       </c>
       <c r="I226">
-        <v>0.7238944420548372</v>
-      </c>
-    </row>
-    <row r="227" spans="1:9">
+        <v>0.72389444205483722</v>
+      </c>
+    </row>
+    <row r="227" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>234</v>
       </c>
@@ -11611,7 +11637,7 @@
         <v>1269</v>
       </c>
       <c r="E227">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F227">
         <v>1</v>
@@ -11620,13 +11646,13 @@
         <v>0.875</v>
       </c>
       <c r="H227">
-        <v>0.33581779770095</v>
+        <v>0.33581779770094999</v>
       </c>
       <c r="I227">
-        <v>0.7598581229515909</v>
-      </c>
-    </row>
-    <row r="228" spans="1:9">
+        <v>0.75985812295159094</v>
+      </c>
+    </row>
+    <row r="228" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>235</v>
       </c>
@@ -11649,13 +11675,13 @@
         <v>1</v>
       </c>
       <c r="H228">
-        <v>0.3960766046204792</v>
+        <v>0.39607660462047922</v>
       </c>
       <c r="I228">
-        <v>0.7178410982931522</v>
-      </c>
-    </row>
-    <row r="229" spans="1:9">
+        <v>0.71784109829315224</v>
+      </c>
+    </row>
+    <row r="229" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>236</v>
       </c>
@@ -11678,13 +11704,13 @@
         <v>1</v>
       </c>
       <c r="H229">
-        <v>0.456385621473778</v>
+        <v>0.45638562147377798</v>
       </c>
       <c r="I229">
-        <v>0.8813690960428487</v>
-      </c>
-    </row>
-    <row r="230" spans="1:9">
+        <v>0.88136909604284874</v>
+      </c>
+    </row>
+    <row r="230" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>237</v>
       </c>
@@ -11698,7 +11724,7 @@
         <v>1272</v>
       </c>
       <c r="E230">
-        <v>0.9999999999666667</v>
+        <v>0.99999999996666666</v>
       </c>
       <c r="F230">
         <v>1</v>
@@ -11707,13 +11733,13 @@
         <v>1</v>
       </c>
       <c r="H230">
-        <v>0.5852541310828497</v>
+        <v>0.58525413108284974</v>
       </c>
       <c r="I230">
-        <v>0.4337247688324402</v>
-      </c>
-    </row>
-    <row r="231" spans="1:9">
+        <v>0.43372476883244021</v>
+      </c>
+    </row>
+    <row r="231" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>238</v>
       </c>
@@ -11727,7 +11753,7 @@
         <v>1273</v>
       </c>
       <c r="E231">
-        <v>0.9999999999666667</v>
+        <v>0.99999999996666666</v>
       </c>
       <c r="F231">
         <v>1</v>
@@ -11736,13 +11762,13 @@
         <v>1</v>
       </c>
       <c r="H231">
-        <v>0.3434153671434205</v>
+        <v>0.34341536714342052</v>
       </c>
       <c r="I231">
         <v>0.6862438862064012</v>
       </c>
     </row>
-    <row r="232" spans="1:9">
+    <row r="232" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>239</v>
       </c>
@@ -11765,13 +11791,13 @@
         <v>1</v>
       </c>
       <c r="H232">
-        <v>0.6291452273888793</v>
+        <v>0.62914522738887935</v>
       </c>
       <c r="I232">
-        <v>0.9908740450059381</v>
-      </c>
-    </row>
-    <row r="233" spans="1:9">
+        <v>0.99087404500593812</v>
+      </c>
+    </row>
+    <row r="233" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
         <v>240</v>
       </c>
@@ -11794,13 +11820,13 @@
         <v>1</v>
       </c>
       <c r="H233">
-        <v>0.4078294232926555</v>
+        <v>0.40782942329265548</v>
       </c>
       <c r="I233">
-        <v>0.9468189809457614</v>
-      </c>
-    </row>
-    <row r="234" spans="1:9">
+        <v>0.94681898094576145</v>
+      </c>
+    </row>
+    <row r="234" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>241</v>
       </c>
@@ -11823,13 +11849,13 @@
         <v>1</v>
       </c>
       <c r="H234">
-        <v>0.6080446434258646</v>
+        <v>0.60804464342586462</v>
       </c>
       <c r="I234">
-        <v>0.4945847888280752</v>
-      </c>
-    </row>
-    <row r="235" spans="1:9">
+        <v>0.49458478882807522</v>
+      </c>
+    </row>
+    <row r="235" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>242</v>
       </c>
@@ -11843,7 +11869,7 @@
         <v>1277</v>
       </c>
       <c r="E235">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F235">
         <v>1</v>
@@ -11852,13 +11878,13 @@
         <v>1</v>
       </c>
       <c r="H235">
-        <v>0.4506345465630349</v>
+        <v>0.45063454656303492</v>
       </c>
       <c r="I235">
-        <v>0.5144688668604203</v>
-      </c>
-    </row>
-    <row r="236" spans="1:9">
+        <v>0.51446886686042026</v>
+      </c>
+    </row>
+    <row r="236" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>243</v>
       </c>
@@ -11872,7 +11898,7 @@
         <v>925</v>
       </c>
       <c r="E236">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F236">
         <v>1</v>
@@ -11887,7 +11913,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="237" spans="1:9">
+    <row r="237" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>244</v>
       </c>
@@ -11901,22 +11927,22 @@
         <v>1278</v>
       </c>
       <c r="E237">
-        <v>0.9999999999666667</v>
+        <v>0.99999999996666666</v>
       </c>
       <c r="F237">
         <v>1</v>
       </c>
       <c r="G237">
-        <v>0.8888888888888888</v>
+        <v>0.88888888888888884</v>
       </c>
       <c r="H237">
-        <v>0.4566677352467451</v>
+        <v>0.45666773524674509</v>
       </c>
       <c r="I237">
         <v>0.7508912563279122</v>
       </c>
     </row>
-    <row r="238" spans="1:9">
+    <row r="238" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>245</v>
       </c>
@@ -11930,7 +11956,7 @@
         <v>1279</v>
       </c>
       <c r="E238">
-        <v>0.9999999999666667</v>
+        <v>0.99999999996666666</v>
       </c>
       <c r="F238">
         <v>1</v>
@@ -11939,13 +11965,13 @@
         <v>1</v>
       </c>
       <c r="H238">
-        <v>0.363860983125574</v>
+        <v>0.36386098312557402</v>
       </c>
       <c r="I238">
         <v>0.517563403088108</v>
       </c>
     </row>
-    <row r="239" spans="1:9">
+    <row r="239" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>246</v>
       </c>
@@ -11959,7 +11985,7 @@
         <v>1280</v>
       </c>
       <c r="E239">
-        <v>0.9999999999666667</v>
+        <v>0.99999999996666666</v>
       </c>
       <c r="F239">
         <v>1</v>
@@ -11968,13 +11994,13 @@
         <v>1</v>
       </c>
       <c r="H239">
-        <v>0.6116240153837532</v>
+        <v>0.61162401538375322</v>
       </c>
       <c r="I239">
         <v>0.6782683371494298</v>
       </c>
     </row>
-    <row r="240" spans="1:9">
+    <row r="240" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
         <v>247</v>
       </c>
@@ -11988,7 +12014,7 @@
         <v>1281</v>
       </c>
       <c r="E240">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F240">
         <v>1</v>
@@ -11997,13 +12023,13 @@
         <v>1</v>
       </c>
       <c r="H240">
-        <v>0.2310035520119604</v>
+        <v>0.23100355201196041</v>
       </c>
       <c r="I240">
-        <v>0.746926390248273</v>
-      </c>
-    </row>
-    <row r="241" spans="1:9">
+        <v>0.74692639024827301</v>
+      </c>
+    </row>
+    <row r="241" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
         <v>248</v>
       </c>
@@ -12017,7 +12043,7 @@
         <v>1282</v>
       </c>
       <c r="E241">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F241">
         <v>1</v>
@@ -12026,13 +12052,13 @@
         <v>1</v>
       </c>
       <c r="H241">
-        <v>0.3601199639163969</v>
+        <v>0.36011996391639689</v>
       </c>
       <c r="I241">
-        <v>0.9276027896722032</v>
-      </c>
-    </row>
-    <row r="242" spans="1:9">
+        <v>0.92760278967220322</v>
+      </c>
+    </row>
+    <row r="242" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
         <v>249</v>
       </c>
@@ -12046,22 +12072,22 @@
         <v>1283</v>
       </c>
       <c r="E242">
-        <v>0.9999999999666667</v>
+        <v>0.99999999996666666</v>
       </c>
       <c r="F242">
         <v>1</v>
       </c>
       <c r="G242">
-        <v>0.8333333333333334</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="H242">
         <v>0.7414098184953678</v>
       </c>
       <c r="I242">
-        <v>0.5607177549520266</v>
-      </c>
-    </row>
-    <row r="243" spans="1:9">
+        <v>0.56071775495202658</v>
+      </c>
+    </row>
+    <row r="243" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
         <v>250</v>
       </c>
@@ -12075,7 +12101,7 @@
         <v>1284</v>
       </c>
       <c r="E243">
-        <v>0.9999999999666667</v>
+        <v>0.99999999996666666</v>
       </c>
       <c r="F243">
         <v>1</v>
@@ -12084,10 +12110,10 @@
         <v>1</v>
       </c>
       <c r="H243">
-        <v>0.4979569178603385</v>
-      </c>
-    </row>
-    <row r="244" spans="1:9">
+        <v>0.49795691786033852</v>
+      </c>
+    </row>
+    <row r="244" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
         <v>251</v>
       </c>
@@ -12110,13 +12136,13 @@
         <v>1</v>
       </c>
       <c r="H244">
-        <v>0.3581138342312563</v>
+        <v>0.35811383423125631</v>
       </c>
       <c r="I244">
-        <v>0.7700505477824784</v>
-      </c>
-    </row>
-    <row r="245" spans="1:9">
+        <v>0.77005054778247839</v>
+      </c>
+    </row>
+    <row r="245" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
         <v>252</v>
       </c>
@@ -12130,22 +12156,22 @@
         <v>1286</v>
       </c>
       <c r="E245">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F245">
         <v>1</v>
       </c>
       <c r="G245">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="H245">
-        <v>0.3462089091095422</v>
+        <v>0.34620890910954222</v>
       </c>
       <c r="I245">
-        <v>0.4913971815575244</v>
-      </c>
-    </row>
-    <row r="246" spans="1:9">
+        <v>0.49139718155752438</v>
+      </c>
+    </row>
+    <row r="246" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
         <v>253</v>
       </c>
@@ -12159,7 +12185,7 @@
         <v>1287</v>
       </c>
       <c r="E246">
-        <v>0.9999999999666667</v>
+        <v>0.99999999996666666</v>
       </c>
       <c r="F246">
         <v>1</v>
@@ -12168,13 +12194,13 @@
         <v>1</v>
       </c>
       <c r="H246">
-        <v>0.6663177362740877</v>
+        <v>0.66631773627408775</v>
       </c>
       <c r="I246">
-        <v>0.462194039279068</v>
-      </c>
-    </row>
-    <row r="247" spans="1:9">
+        <v>0.46219403927906799</v>
+      </c>
+    </row>
+    <row r="247" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
         <v>254</v>
       </c>
@@ -12188,7 +12214,7 @@
         <v>1288</v>
       </c>
       <c r="E247">
-        <v>0.9999999999666667</v>
+        <v>0.99999999996666666</v>
       </c>
       <c r="F247">
         <v>1</v>
@@ -12197,13 +12223,13 @@
         <v>1</v>
       </c>
       <c r="H247">
-        <v>0.4825474142628942</v>
+        <v>0.48254741426289421</v>
       </c>
       <c r="I247">
         <v>0.5504229904908664</v>
       </c>
     </row>
-    <row r="248" spans="1:9">
+    <row r="248" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
         <v>255</v>
       </c>
@@ -12217,7 +12243,7 @@
         <v>1289</v>
       </c>
       <c r="E248">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F248">
         <v>1</v>
@@ -12229,10 +12255,10 @@
         <v>0.2132208734505813</v>
       </c>
       <c r="I248">
-        <v>0.6893311202257166</v>
-      </c>
-    </row>
-    <row r="249" spans="1:9">
+        <v>0.68933112022571663</v>
+      </c>
+    </row>
+    <row r="249" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
         <v>256</v>
       </c>
@@ -12246,7 +12272,7 @@
         <v>1290</v>
       </c>
       <c r="E249">
-        <v>0.9999999999666667</v>
+        <v>0.99999999996666666</v>
       </c>
       <c r="F249">
         <v>1</v>
@@ -12255,13 +12281,13 @@
         <v>1</v>
       </c>
       <c r="H249">
-        <v>0.5420658109618511</v>
+        <v>0.54206581096185114</v>
       </c>
       <c r="I249">
-        <v>0.6299098707501287</v>
-      </c>
-    </row>
-    <row r="250" spans="1:9">
+        <v>0.62990987075012872</v>
+      </c>
+    </row>
+    <row r="250" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
         <v>257</v>
       </c>
@@ -12284,13 +12310,13 @@
         <v>1</v>
       </c>
       <c r="H250">
-        <v>0.6973159338942699</v>
+        <v>0.69731593389426993</v>
       </c>
       <c r="I250">
-        <v>0.7006066676173872</v>
-      </c>
-    </row>
-    <row r="251" spans="1:9">
+        <v>0.70060666761738721</v>
+      </c>
+    </row>
+    <row r="251" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
         <v>258</v>
       </c>
@@ -12304,7 +12330,7 @@
         <v>1292</v>
       </c>
       <c r="E251">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F251">
         <v>1</v>
@@ -12313,13 +12339,13 @@
         <v>1</v>
       </c>
       <c r="H251">
-        <v>0.4325112790565303</v>
+        <v>0.43251127905653031</v>
       </c>
       <c r="I251">
-        <v>0.6023430463554831</v>
-      </c>
-    </row>
-    <row r="252" spans="1:9">
+        <v>0.60234304635548308</v>
+      </c>
+    </row>
+    <row r="252" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
         <v>259</v>
       </c>
@@ -12333,7 +12359,7 @@
         <v>1293</v>
       </c>
       <c r="E252">
-        <v>0.8333333332916666</v>
+        <v>0.83333333329166659</v>
       </c>
       <c r="F252">
         <v>1</v>
@@ -12342,13 +12368,13 @@
         <v>1</v>
       </c>
       <c r="H252">
-        <v>0.4858074658515308</v>
+        <v>0.48580746585153078</v>
       </c>
       <c r="I252">
-        <v>0.4198600561732203</v>
-      </c>
-    </row>
-    <row r="253" spans="1:9">
+        <v>0.41986005617322031</v>
+      </c>
+    </row>
+    <row r="253" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
         <v>260</v>
       </c>
@@ -12362,7 +12388,7 @@
         <v>1294</v>
       </c>
       <c r="E253">
-        <v>0.9999999999666667</v>
+        <v>0.99999999996666666</v>
       </c>
       <c r="F253">
         <v>1</v>
@@ -12371,13 +12397,13 @@
         <v>0.8</v>
       </c>
       <c r="H253">
-        <v>0.7818081257102352</v>
+        <v>0.78180812571023517</v>
       </c>
       <c r="I253">
-        <v>0.619990891740956</v>
-      </c>
-    </row>
-    <row r="254" spans="1:9">
+        <v>0.61999089174095601</v>
+      </c>
+    </row>
+    <row r="254" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
         <v>261</v>
       </c>
@@ -12391,7 +12417,7 @@
         <v>1295</v>
       </c>
       <c r="E254">
-        <v>0.9999999999666667</v>
+        <v>0.99999999996666666</v>
       </c>
       <c r="F254">
         <v>1</v>
@@ -12400,13 +12426,13 @@
         <v>1</v>
       </c>
       <c r="H254">
-        <v>0.4871788695935219</v>
+        <v>0.48717886959352191</v>
       </c>
       <c r="I254">
-        <v>0.4655368934057376</v>
-      </c>
-    </row>
-    <row r="255" spans="1:9">
+        <v>0.46553689340573762</v>
+      </c>
+    </row>
+    <row r="255" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
         <v>262</v>
       </c>
@@ -12420,7 +12446,7 @@
         <v>1296</v>
       </c>
       <c r="E255">
-        <v>0.9999999999666667</v>
+        <v>0.99999999996666666</v>
       </c>
       <c r="F255">
         <v>1</v>
@@ -12429,13 +12455,13 @@
         <v>0.75</v>
       </c>
       <c r="H255">
-        <v>0.3879529656443876</v>
+        <v>0.38795296564438758</v>
       </c>
       <c r="I255">
-        <v>0.4695489664792312</v>
-      </c>
-    </row>
-    <row r="256" spans="1:9">
+        <v>0.46954896647923122</v>
+      </c>
+    </row>
+    <row r="256" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
         <v>263</v>
       </c>
@@ -12458,13 +12484,13 @@
         <v>1</v>
       </c>
       <c r="H256">
-        <v>0.750716286670957</v>
+        <v>0.75071628667095702</v>
       </c>
       <c r="I256">
-        <v>0.8780184469647139</v>
-      </c>
-    </row>
-    <row r="257" spans="1:9">
+        <v>0.87801844696471387</v>
+      </c>
+    </row>
+    <row r="257" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
         <v>264</v>
       </c>
@@ -12478,7 +12504,7 @@
         <v>1298</v>
       </c>
       <c r="E257">
-        <v>0.9999999999666667</v>
+        <v>0.99999999996666666</v>
       </c>
       <c r="F257">
         <v>1</v>
@@ -12487,13 +12513,13 @@
         <v>1</v>
       </c>
       <c r="H257">
-        <v>0.4133710132707801</v>
+        <v>0.41337101327078007</v>
       </c>
       <c r="I257">
-        <v>0.8137484912905381</v>
-      </c>
-    </row>
-    <row r="258" spans="1:9">
+        <v>0.81374849129053806</v>
+      </c>
+    </row>
+    <row r="258" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
         <v>265</v>
       </c>
@@ -12507,7 +12533,7 @@
         <v>1299</v>
       </c>
       <c r="E258">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F258">
         <v>1</v>
@@ -12516,13 +12542,13 @@
         <v>0.875</v>
       </c>
       <c r="H258">
-        <v>0.5940295153578538</v>
+        <v>0.59402951535785375</v>
       </c>
       <c r="I258">
-        <v>0.7659988637287918</v>
-      </c>
-    </row>
-    <row r="259" spans="1:9">
+        <v>0.76599886372879178</v>
+      </c>
+    </row>
+    <row r="259" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
         <v>266</v>
       </c>
@@ -12536,7 +12562,7 @@
         <v>1300</v>
       </c>
       <c r="E259">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F259">
         <v>1</v>
@@ -12545,13 +12571,13 @@
         <v>1</v>
       </c>
       <c r="H259">
-        <v>0.2534209031039544</v>
+        <v>0.25342090310395438</v>
       </c>
       <c r="I259">
-        <v>0.6261550727118437</v>
-      </c>
-    </row>
-    <row r="260" spans="1:9">
+        <v>0.62615507271184367</v>
+      </c>
+    </row>
+    <row r="260" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
         <v>267</v>
       </c>
@@ -12565,7 +12591,7 @@
         <v>1301</v>
       </c>
       <c r="E260">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F260">
         <v>1</v>
@@ -12574,13 +12600,13 @@
         <v>0.5</v>
       </c>
       <c r="H260">
-        <v>0.5531474244642163</v>
+        <v>0.55314742446421628</v>
       </c>
       <c r="I260">
-        <v>0.5349463801301304</v>
-      </c>
-    </row>
-    <row r="261" spans="1:9">
+        <v>0.53494638013013041</v>
+      </c>
+    </row>
+    <row r="261" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
         <v>268</v>
       </c>
@@ -12594,7 +12620,7 @@
         <v>1302</v>
       </c>
       <c r="E261">
-        <v>0.9999999999666667</v>
+        <v>0.99999999996666666</v>
       </c>
       <c r="F261">
         <v>1</v>
@@ -12606,10 +12632,10 @@
         <v>0.6229388378131312</v>
       </c>
       <c r="I261">
-        <v>0.9200780424473363</v>
-      </c>
-    </row>
-    <row r="262" spans="1:9">
+        <v>0.92007804244733626</v>
+      </c>
+    </row>
+    <row r="262" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
         <v>269</v>
       </c>
@@ -12623,22 +12649,22 @@
         <v>1303</v>
       </c>
       <c r="E262">
-        <v>0.8333333332916666</v>
+        <v>0.83333333329166659</v>
       </c>
       <c r="F262">
         <v>1</v>
       </c>
       <c r="G262">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="H262">
-        <v>0.5190374884713118</v>
+        <v>0.51903748847131181</v>
       </c>
       <c r="I262">
-        <v>0.8129169697036662</v>
-      </c>
-    </row>
-    <row r="263" spans="1:9">
+        <v>0.81291696970366623</v>
+      </c>
+    </row>
+    <row r="263" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
         <v>270</v>
       </c>
@@ -12652,7 +12678,7 @@
         <v>1304</v>
       </c>
       <c r="E263">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F263">
         <v>1</v>
@@ -12661,13 +12687,13 @@
         <v>1</v>
       </c>
       <c r="H263">
-        <v>0.6172784961424805</v>
+        <v>0.61727849614248054</v>
       </c>
       <c r="I263">
-        <v>0.8712159299254396</v>
-      </c>
-    </row>
-    <row r="264" spans="1:9">
+        <v>0.87121592992543961</v>
+      </c>
+    </row>
+    <row r="264" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
         <v>271</v>
       </c>
@@ -12681,7 +12707,7 @@
         <v>1305</v>
       </c>
       <c r="E264">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F264">
         <v>1</v>
@@ -12690,13 +12716,13 @@
         <v>1</v>
       </c>
       <c r="H264">
-        <v>0.3658464878530195</v>
+        <v>0.36584648785301949</v>
       </c>
       <c r="I264">
-        <v>0.9648914922122129</v>
-      </c>
-    </row>
-    <row r="265" spans="1:9">
+        <v>0.96489149221221293</v>
+      </c>
+    </row>
+    <row r="265" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
         <v>272</v>
       </c>
@@ -12710,7 +12736,7 @@
         <v>954</v>
       </c>
       <c r="E265">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F265">
         <v>1</v>
@@ -12725,7 +12751,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="266" spans="1:9">
+    <row r="266" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
         <v>273</v>
       </c>
@@ -12739,7 +12765,7 @@
         <v>1306</v>
       </c>
       <c r="E266">
-        <v>0.9999999999666667</v>
+        <v>0.99999999996666666</v>
       </c>
       <c r="F266">
         <v>1</v>
@@ -12748,13 +12774,13 @@
         <v>1</v>
       </c>
       <c r="H266">
-        <v>0.6477442018760214</v>
+        <v>0.64774420187602144</v>
       </c>
       <c r="I266">
-        <v>0.9854790151141128</v>
-      </c>
-    </row>
-    <row r="267" spans="1:9">
+        <v>0.98547901511411284</v>
+      </c>
+    </row>
+    <row r="267" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
         <v>274</v>
       </c>
@@ -12768,7 +12794,7 @@
         <v>1307</v>
       </c>
       <c r="E267">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F267">
         <v>1</v>
@@ -12777,13 +12803,13 @@
         <v>1</v>
       </c>
       <c r="H267">
-        <v>0.5132952285419145</v>
+        <v>0.51329522854191445</v>
       </c>
       <c r="I267">
-        <v>0.9578092570681047</v>
-      </c>
-    </row>
-    <row r="268" spans="1:9">
+        <v>0.95780925706810471</v>
+      </c>
+    </row>
+    <row r="268" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
         <v>275</v>
       </c>
@@ -12797,7 +12823,7 @@
         <v>957</v>
       </c>
       <c r="E268">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F268">
         <v>1</v>
@@ -12806,13 +12832,13 @@
         <v>1</v>
       </c>
       <c r="H268">
-        <v>0.2732083776524125</v>
+        <v>0.27320837765241252</v>
       </c>
       <c r="I268">
         <v>1</v>
       </c>
     </row>
-    <row r="269" spans="1:9">
+    <row r="269" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
         <v>276</v>
       </c>
@@ -12835,13 +12861,13 @@
         <v>1</v>
       </c>
       <c r="H269">
-        <v>0.5217639626943421</v>
+        <v>0.52176396269434211</v>
       </c>
       <c r="I269">
-        <v>0.5819193243882337</v>
-      </c>
-    </row>
-    <row r="270" spans="1:9">
+        <v>0.58191932438823368</v>
+      </c>
+    </row>
+    <row r="270" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
         <v>277</v>
       </c>
@@ -12855,22 +12881,22 @@
         <v>1309</v>
       </c>
       <c r="E270">
-        <v>0.8333333332916666</v>
+        <v>0.83333333329166659</v>
       </c>
       <c r="F270">
         <v>1</v>
       </c>
       <c r="G270">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="H270">
-        <v>0.5454182284595733</v>
+        <v>0.54541822845957333</v>
       </c>
       <c r="I270">
-        <v>0.761784986851807</v>
-      </c>
-    </row>
-    <row r="271" spans="1:9">
+        <v>0.76178498685180696</v>
+      </c>
+    </row>
+    <row r="271" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
         <v>278</v>
       </c>
@@ -12893,13 +12919,13 @@
         <v>1</v>
       </c>
       <c r="H271">
-        <v>0.5062981149913173</v>
+        <v>0.50629811499131727</v>
       </c>
       <c r="I271">
-        <v>0.6293115430050712</v>
-      </c>
-    </row>
-    <row r="272" spans="1:9">
+        <v>0.62931154300507119</v>
+      </c>
+    </row>
+    <row r="272" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
         <v>279</v>
       </c>
@@ -12913,22 +12939,22 @@
         <v>1311</v>
       </c>
       <c r="E272">
-        <v>0.9999999999666667</v>
+        <v>0.99999999996666666</v>
       </c>
       <c r="F272">
         <v>1</v>
       </c>
       <c r="G272">
-        <v>0.8888888888888888</v>
+        <v>0.88888888888888884</v>
       </c>
       <c r="H272">
-        <v>0.4856550257246892</v>
+        <v>0.48565502572468922</v>
       </c>
       <c r="I272">
-        <v>0.635120255005987</v>
-      </c>
-    </row>
-    <row r="273" spans="1:9">
+        <v>0.63512025500598701</v>
+      </c>
+    </row>
+    <row r="273" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
         <v>280</v>
       </c>
@@ -12942,22 +12968,22 @@
         <v>1312</v>
       </c>
       <c r="E273">
-        <v>0.8333333332916666</v>
+        <v>0.83333333329166659</v>
       </c>
       <c r="F273">
         <v>1</v>
       </c>
       <c r="G273">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="H273">
-        <v>0.7194145994444804</v>
+        <v>0.71941459944448038</v>
       </c>
       <c r="I273">
-        <v>0.614009264229627</v>
-      </c>
-    </row>
-    <row r="274" spans="1:9">
+        <v>0.61400926422962698</v>
+      </c>
+    </row>
+    <row r="274" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
         <v>281</v>
       </c>
@@ -12971,22 +12997,22 @@
         <v>1313</v>
       </c>
       <c r="E274">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F274">
         <v>1</v>
       </c>
       <c r="G274">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="H274">
-        <v>0.5559006171015675</v>
+        <v>0.55590061710156746</v>
       </c>
       <c r="I274">
-        <v>0.6312748601081672</v>
-      </c>
-    </row>
-    <row r="275" spans="1:9">
+        <v>0.63127486010816725</v>
+      </c>
+    </row>
+    <row r="275" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
         <v>282</v>
       </c>
@@ -13009,13 +13035,13 @@
         <v>0.75</v>
       </c>
       <c r="H275">
-        <v>0.3542067046822256</v>
+        <v>0.35420670468222559</v>
       </c>
       <c r="I275">
-        <v>0.9702802903258829</v>
-      </c>
-    </row>
-    <row r="276" spans="1:9">
+        <v>0.97028029032588292</v>
+      </c>
+    </row>
+    <row r="276" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
         <v>283</v>
       </c>
@@ -13029,7 +13055,7 @@
         <v>1315</v>
       </c>
       <c r="E276">
-        <v>0.9999999999666667</v>
+        <v>0.99999999996666666</v>
       </c>
       <c r="F276">
         <v>1</v>
@@ -13038,13 +13064,13 @@
         <v>0.4</v>
       </c>
       <c r="H276">
-        <v>0.7484192150054012</v>
+        <v>0.74841921500540121</v>
       </c>
       <c r="I276">
-        <v>0.8591643096743702</v>
-      </c>
-    </row>
-    <row r="277" spans="1:9">
+        <v>0.85916430967437019</v>
+      </c>
+    </row>
+    <row r="277" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
         <v>284</v>
       </c>
@@ -13058,22 +13084,22 @@
         <v>1316</v>
       </c>
       <c r="E277">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F277">
         <v>1</v>
       </c>
       <c r="G277">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="H277">
-        <v>0.4771268780608682</v>
+        <v>0.47712687806086818</v>
       </c>
       <c r="I277">
-        <v>0.5263813902824699</v>
-      </c>
-    </row>
-    <row r="278" spans="1:9">
+        <v>0.52638139028246989</v>
+      </c>
+    </row>
+    <row r="278" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
         <v>285</v>
       </c>
@@ -13096,13 +13122,13 @@
         <v>0.8</v>
       </c>
       <c r="H278">
-        <v>0.4771032176285759</v>
+        <v>0.47710321762857588</v>
       </c>
       <c r="I278">
-        <v>0.5969734116514072</v>
-      </c>
-    </row>
-    <row r="279" spans="1:9">
+        <v>0.59697341165140716</v>
+      </c>
+    </row>
+    <row r="279" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
         <v>286</v>
       </c>
@@ -13116,7 +13142,7 @@
         <v>1318</v>
       </c>
       <c r="E279">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F279">
         <v>1</v>
@@ -13125,13 +13151,13 @@
         <v>0.25</v>
       </c>
       <c r="H279">
-        <v>0.5627354397033126</v>
+        <v>0.56273543970331263</v>
       </c>
       <c r="I279">
-        <v>0.6199289511705163</v>
-      </c>
-    </row>
-    <row r="280" spans="1:9">
+        <v>0.61992895117051627</v>
+      </c>
+    </row>
+    <row r="280" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
         <v>287</v>
       </c>
@@ -13145,22 +13171,22 @@
         <v>1319</v>
       </c>
       <c r="E280">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F280">
         <v>1</v>
       </c>
       <c r="G280">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="H280">
-        <v>0.4174655612892026</v>
+        <v>0.41746556128920259</v>
       </c>
       <c r="I280">
-        <v>0.8161145716174227</v>
-      </c>
-    </row>
-    <row r="281" spans="1:9">
+        <v>0.81611457161742273</v>
+      </c>
+    </row>
+    <row r="281" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
         <v>288</v>
       </c>
@@ -13183,13 +13209,13 @@
         <v>1</v>
       </c>
       <c r="H281">
-        <v>0.6252979542657202</v>
+        <v>0.62529795426572021</v>
       </c>
       <c r="I281">
-        <v>0.5371621136900747</v>
-      </c>
-    </row>
-    <row r="282" spans="1:9">
+        <v>0.53716211369007472</v>
+      </c>
+    </row>
+    <row r="282" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
         <v>289</v>
       </c>
@@ -13203,7 +13229,7 @@
         <v>1321</v>
       </c>
       <c r="E282">
-        <v>0.9999999999666667</v>
+        <v>0.99999999996666666</v>
       </c>
       <c r="F282">
         <v>1</v>
@@ -13212,13 +13238,13 @@
         <v>1</v>
       </c>
       <c r="H282">
-        <v>0.7048066575155389</v>
+        <v>0.70480665751553895</v>
       </c>
       <c r="I282">
-        <v>0.9389879228082554</v>
-      </c>
-    </row>
-    <row r="283" spans="1:9">
+        <v>0.93898792280825538</v>
+      </c>
+    </row>
+    <row r="283" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
         <v>290</v>
       </c>
@@ -13232,7 +13258,7 @@
         <v>1322</v>
       </c>
       <c r="E283">
-        <v>0.9999999999666667</v>
+        <v>0.99999999996666666</v>
       </c>
       <c r="F283">
         <v>1</v>
@@ -13241,13 +13267,13 @@
         <v>1</v>
       </c>
       <c r="H283">
-        <v>0.4502686094579011</v>
+        <v>0.45026860945790109</v>
       </c>
       <c r="I283">
-        <v>0.6762504573917398</v>
-      </c>
-    </row>
-    <row r="284" spans="1:9">
+        <v>0.67625045739173983</v>
+      </c>
+    </row>
+    <row r="284" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
         <v>291</v>
       </c>
@@ -13261,7 +13287,7 @@
         <v>1323</v>
       </c>
       <c r="E284">
-        <v>0.9999999999666667</v>
+        <v>0.99999999996666666</v>
       </c>
       <c r="F284">
         <v>1</v>
@@ -13270,13 +13296,13 @@
         <v>1</v>
       </c>
       <c r="H284">
-        <v>0.3473764157982226</v>
+        <v>0.34737641579822259</v>
       </c>
       <c r="I284">
-        <v>0.7351142443468199</v>
-      </c>
-    </row>
-    <row r="285" spans="1:9">
+        <v>0.73511424434681993</v>
+      </c>
+    </row>
+    <row r="285" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
         <v>292</v>
       </c>
@@ -13290,7 +13316,7 @@
         <v>1324</v>
       </c>
       <c r="E285">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F285">
         <v>1</v>
@@ -13299,13 +13325,13 @@
         <v>0.6</v>
       </c>
       <c r="H285">
-        <v>0.3897014132095664</v>
+        <v>0.38970141320956642</v>
       </c>
       <c r="I285">
-        <v>0.8022945097054793</v>
-      </c>
-    </row>
-    <row r="286" spans="1:9">
+        <v>0.80229450970547933</v>
+      </c>
+    </row>
+    <row r="286" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
         <v>293</v>
       </c>
@@ -13319,7 +13345,7 @@
         <v>1325</v>
       </c>
       <c r="E286">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F286">
         <v>1</v>
@@ -13328,13 +13354,13 @@
         <v>1</v>
       </c>
       <c r="H286">
-        <v>0.3127841055631468</v>
+        <v>0.31278410556314679</v>
       </c>
       <c r="I286">
-        <v>0.1315006412836298</v>
-      </c>
-    </row>
-    <row r="287" spans="1:9">
+        <v>0.13150064128362979</v>
+      </c>
+    </row>
+    <row r="287" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
         <v>294</v>
       </c>
@@ -13348,7 +13374,7 @@
         <v>1326</v>
       </c>
       <c r="E287">
-        <v>0.8333333332916666</v>
+        <v>0.83333333329166659</v>
       </c>
       <c r="F287">
         <v>1</v>
@@ -13357,13 +13383,13 @@
         <v>1</v>
       </c>
       <c r="H287">
-        <v>0.7248937698752581</v>
+        <v>0.72489376987525811</v>
       </c>
       <c r="I287">
-        <v>0.5362170499710167</v>
-      </c>
-    </row>
-    <row r="288" spans="1:9">
+        <v>0.53621704997101671</v>
+      </c>
+    </row>
+    <row r="288" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
         <v>295</v>
       </c>
@@ -13377,7 +13403,7 @@
         <v>1327</v>
       </c>
       <c r="E288">
-        <v>0.9999999999666667</v>
+        <v>0.99999999996666666</v>
       </c>
       <c r="F288">
         <v>1</v>
@@ -13386,13 +13412,13 @@
         <v>1</v>
       </c>
       <c r="H288">
-        <v>0.5130733483786928</v>
+        <v>0.51307334837869278</v>
       </c>
       <c r="I288">
-        <v>0.9764312864805961</v>
-      </c>
-    </row>
-    <row r="289" spans="1:9">
+        <v>0.97643128648059607</v>
+      </c>
+    </row>
+    <row r="289" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
         <v>296</v>
       </c>
@@ -13406,7 +13432,7 @@
         <v>1328</v>
       </c>
       <c r="E289">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F289">
         <v>1</v>
@@ -13418,10 +13444,10 @@
         <v>0.5412357594385554</v>
       </c>
       <c r="I289">
-        <v>0.6690128761816057</v>
-      </c>
-    </row>
-    <row r="290" spans="1:9">
+        <v>0.66901287618160565</v>
+      </c>
+    </row>
+    <row r="290" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
         <v>297</v>
       </c>
@@ -13444,13 +13470,13 @@
         <v>1</v>
       </c>
       <c r="H290">
-        <v>0.3086870352193627</v>
+        <v>0.30868703521936269</v>
       </c>
       <c r="I290">
-        <v>0.8463671115128986</v>
-      </c>
-    </row>
-    <row r="291" spans="1:9">
+        <v>0.84636711151289856</v>
+      </c>
+    </row>
+    <row r="291" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
         <v>298</v>
       </c>
@@ -13464,19 +13490,19 @@
         <v>1330</v>
       </c>
       <c r="E291">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F291">
         <v>1</v>
       </c>
       <c r="G291">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="H291">
-        <v>0.4457392028533801</v>
-      </c>
-    </row>
-    <row r="292" spans="1:9">
+        <v>0.44573920285338009</v>
+      </c>
+    </row>
+    <row r="292" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
         <v>299</v>
       </c>
@@ -13490,7 +13516,7 @@
         <v>1331</v>
       </c>
       <c r="E292">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F292">
         <v>1</v>
@@ -13499,13 +13525,13 @@
         <v>0.5</v>
       </c>
       <c r="H292">
-        <v>0.5248257523154931</v>
+        <v>0.52482575231549311</v>
       </c>
       <c r="I292">
         <v>0.490572385773419</v>
       </c>
     </row>
-    <row r="293" spans="1:9">
+    <row r="293" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
         <v>300</v>
       </c>
@@ -13519,7 +13545,7 @@
         <v>1332</v>
       </c>
       <c r="E293">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F293">
         <v>1</v>
@@ -13528,13 +13554,13 @@
         <v>1</v>
       </c>
       <c r="H293">
-        <v>0.569744116626684</v>
+        <v>0.56974411662668401</v>
       </c>
       <c r="I293">
-        <v>0.6772637435894717</v>
-      </c>
-    </row>
-    <row r="294" spans="1:9">
+        <v>0.67726374358947172</v>
+      </c>
+    </row>
+    <row r="294" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
         <v>301</v>
       </c>
@@ -13557,13 +13583,13 @@
         <v>1</v>
       </c>
       <c r="H294">
-        <v>0.4449685762003809</v>
+        <v>0.44496857620038088</v>
       </c>
       <c r="I294">
-        <v>0.6675209917058353</v>
-      </c>
-    </row>
-    <row r="295" spans="1:9">
+        <v>0.66752099170583534</v>
+      </c>
+    </row>
+    <row r="295" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
         <v>302</v>
       </c>
@@ -13583,16 +13609,16 @@
         <v>1</v>
       </c>
       <c r="G295">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="H295">
-        <v>0.5218777771016052</v>
+        <v>0.52187777710160521</v>
       </c>
       <c r="I295">
-        <v>0.6364818165209116</v>
-      </c>
-    </row>
-    <row r="296" spans="1:9">
+        <v>0.63648181652091163</v>
+      </c>
+    </row>
+    <row r="296" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
         <v>303</v>
       </c>
@@ -13606,7 +13632,7 @@
         <v>1335</v>
       </c>
       <c r="E296">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F296">
         <v>1</v>
@@ -13615,10 +13641,10 @@
         <v>1</v>
       </c>
       <c r="H296">
-        <v>0.5004923603791441</v>
-      </c>
-    </row>
-    <row r="297" spans="1:9">
+        <v>0.50049236037914413</v>
+      </c>
+    </row>
+    <row r="297" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
         <v>304</v>
       </c>
@@ -13632,7 +13658,7 @@
         <v>1336</v>
       </c>
       <c r="E297">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F297">
         <v>1</v>
@@ -13644,10 +13670,10 @@
         <v>0.7788118543103264</v>
       </c>
       <c r="I297">
-        <v>0.8130046872314289</v>
-      </c>
-    </row>
-    <row r="298" spans="1:9">
+        <v>0.81300468723142894</v>
+      </c>
+    </row>
+    <row r="298" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
         <v>305</v>
       </c>
@@ -13673,10 +13699,10 @@
         <v>0.2829180365744402</v>
       </c>
       <c r="I298">
-        <v>0.9201283412636019</v>
-      </c>
-    </row>
-    <row r="299" spans="1:9">
+        <v>0.92012834126360188</v>
+      </c>
+    </row>
+    <row r="299" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
         <v>306</v>
       </c>
@@ -13690,7 +13716,7 @@
         <v>1338</v>
       </c>
       <c r="E299">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F299">
         <v>1</v>
@@ -13705,7 +13731,7 @@
         <v>0.7035438357733268</v>
       </c>
     </row>
-    <row r="300" spans="1:9">
+    <row r="300" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
         <v>307</v>
       </c>
@@ -13719,22 +13745,22 @@
         <v>1339</v>
       </c>
       <c r="E300">
-        <v>0.8333333332916666</v>
+        <v>0.83333333329166659</v>
       </c>
       <c r="F300">
         <v>1</v>
       </c>
       <c r="G300">
-        <v>0.8333333333333334</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="H300">
-        <v>0.3741111554109788</v>
+        <v>0.37411115541097878</v>
       </c>
       <c r="I300">
         <v>0.5094446413624284</v>
       </c>
     </row>
-    <row r="301" spans="1:9">
+    <row r="301" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
         <v>308</v>
       </c>
@@ -13748,7 +13774,7 @@
         <v>990</v>
       </c>
       <c r="E301">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F301">
         <v>1</v>
@@ -13757,13 +13783,13 @@
         <v>0.5</v>
       </c>
       <c r="H301">
-        <v>0.342470297436447</v>
+        <v>0.34247029743644702</v>
       </c>
       <c r="I301">
         <v>1</v>
       </c>
     </row>
-    <row r="302" spans="1:9">
+    <row r="302" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
         <v>309</v>
       </c>
@@ -13777,7 +13803,7 @@
         <v>1340</v>
       </c>
       <c r="E302">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F302">
         <v>1</v>
@@ -13789,10 +13815,10 @@
         <v>0.4718483748116879</v>
       </c>
       <c r="I302">
-        <v>0.7841042643774113</v>
-      </c>
-    </row>
-    <row r="303" spans="1:9">
+        <v>0.78410426437741132</v>
+      </c>
+    </row>
+    <row r="303" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
         <v>310</v>
       </c>
@@ -13806,7 +13832,7 @@
         <v>1341</v>
       </c>
       <c r="E303">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F303">
         <v>1</v>
@@ -13815,13 +13841,13 @@
         <v>0</v>
       </c>
       <c r="H303">
-        <v>0.6135189083465238</v>
+        <v>0.61351890834652378</v>
       </c>
       <c r="I303">
         <v>0.5746426272551759</v>
       </c>
     </row>
-    <row r="304" spans="1:9">
+    <row r="304" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
         <v>311</v>
       </c>
@@ -13835,7 +13861,7 @@
         <v>1342</v>
       </c>
       <c r="E304">
-        <v>0.9999999999666667</v>
+        <v>0.99999999996666666</v>
       </c>
       <c r="F304">
         <v>1</v>
@@ -13844,13 +13870,13 @@
         <v>0</v>
       </c>
       <c r="H304">
-        <v>0.6019107455005011</v>
+        <v>0.60191074550050105</v>
       </c>
       <c r="I304">
-        <v>0.4947626020481419</v>
-      </c>
-    </row>
-    <row r="305" spans="1:9">
+        <v>0.49476260204814188</v>
+      </c>
+    </row>
+    <row r="305" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
         <v>312</v>
       </c>
@@ -13864,7 +13890,7 @@
         <v>1343</v>
       </c>
       <c r="E305">
-        <v>0.9999999999666667</v>
+        <v>0.99999999996666666</v>
       </c>
       <c r="F305">
         <v>1</v>
@@ -13873,13 +13899,13 @@
         <v>0.5</v>
       </c>
       <c r="H305">
-        <v>0.4621913115815297</v>
+        <v>0.46219131158152971</v>
       </c>
       <c r="I305">
-        <v>0.3412186761419496</v>
-      </c>
-    </row>
-    <row r="306" spans="1:9">
+        <v>0.34121867614194962</v>
+      </c>
+    </row>
+    <row r="306" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
         <v>313</v>
       </c>
@@ -13893,7 +13919,7 @@
         <v>1344</v>
       </c>
       <c r="E306">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F306">
         <v>1</v>
@@ -13902,13 +13928,13 @@
         <v>1</v>
       </c>
       <c r="H306">
-        <v>0.3972162209276313</v>
+        <v>0.39721622092763131</v>
       </c>
       <c r="I306">
-        <v>0.5420691030821386</v>
-      </c>
-    </row>
-    <row r="307" spans="1:9">
+        <v>0.54206910308213863</v>
+      </c>
+    </row>
+    <row r="307" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
         <v>314</v>
       </c>
@@ -13922,7 +13948,7 @@
         <v>1345</v>
       </c>
       <c r="E307">
-        <v>0.9999999999666667</v>
+        <v>0.99999999996666666</v>
       </c>
       <c r="F307">
         <v>1</v>
@@ -13931,13 +13957,13 @@
         <v>0.8</v>
       </c>
       <c r="H307">
-        <v>0.5579605434482164</v>
+        <v>0.55796054344821644</v>
       </c>
       <c r="I307">
-        <v>0.6735405703762143</v>
-      </c>
-    </row>
-    <row r="308" spans="1:9">
+        <v>0.67354057037621429</v>
+      </c>
+    </row>
+    <row r="308" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
         <v>315</v>
       </c>
@@ -13951,22 +13977,22 @@
         <v>1346</v>
       </c>
       <c r="E308">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F308">
         <v>1</v>
       </c>
       <c r="G308">
-        <v>0.8888888888888888</v>
+        <v>0.88888888888888884</v>
       </c>
       <c r="H308">
-        <v>0.4441135713519512</v>
+        <v>0.44411357135195118</v>
       </c>
       <c r="I308">
-        <v>0.4250145293122264</v>
-      </c>
-    </row>
-    <row r="309" spans="1:9">
+        <v>0.42501452931222639</v>
+      </c>
+    </row>
+    <row r="309" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
         <v>316</v>
       </c>
@@ -13980,7 +14006,7 @@
         <v>1347</v>
       </c>
       <c r="E309">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F309">
         <v>1</v>
@@ -13992,10 +14018,10 @@
         <v>0.5138665003023053</v>
       </c>
       <c r="I309">
-        <v>0.6666393950163159</v>
-      </c>
-    </row>
-    <row r="310" spans="1:9">
+        <v>0.66663939501631586</v>
+      </c>
+    </row>
+    <row r="310" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
         <v>317</v>
       </c>
@@ -14009,7 +14035,7 @@
         <v>1348</v>
       </c>
       <c r="E310">
-        <v>0.9999999999666667</v>
+        <v>0.99999999996666666</v>
       </c>
       <c r="F310">
         <v>1</v>
@@ -14018,13 +14044,13 @@
         <v>1</v>
       </c>
       <c r="H310">
-        <v>0.526832527277842</v>
+        <v>0.52683252727784202</v>
       </c>
       <c r="I310">
-        <v>0.6783692853502878</v>
-      </c>
-    </row>
-    <row r="311" spans="1:9">
+        <v>0.67836928535028784</v>
+      </c>
+    </row>
+    <row r="311" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
         <v>318</v>
       </c>
@@ -14038,7 +14064,7 @@
         <v>1349</v>
       </c>
       <c r="E311">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F311">
         <v>1</v>
@@ -14047,13 +14073,13 @@
         <v>1</v>
       </c>
       <c r="H311">
-        <v>0.3860654368838856</v>
+        <v>0.38606543688388562</v>
       </c>
       <c r="I311">
-        <v>0.467627678066256</v>
-      </c>
-    </row>
-    <row r="312" spans="1:9">
+        <v>0.46762767806625599</v>
+      </c>
+    </row>
+    <row r="312" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
         <v>319</v>
       </c>
@@ -14067,7 +14093,7 @@
         <v>1350</v>
       </c>
       <c r="E312">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F312">
         <v>1</v>
@@ -14076,13 +14102,13 @@
         <v>1</v>
       </c>
       <c r="H312">
-        <v>0.4473930432785461</v>
+        <v>0.44739304327854612</v>
       </c>
       <c r="I312">
-        <v>0.6458860768802587</v>
-      </c>
-    </row>
-    <row r="313" spans="1:9">
+        <v>0.64588607688025867</v>
+      </c>
+    </row>
+    <row r="313" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
         <v>320</v>
       </c>
@@ -14096,7 +14122,7 @@
         <v>1351</v>
       </c>
       <c r="E313">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F313">
         <v>1</v>
@@ -14108,10 +14134,10 @@
         <v>0.5292249721745349</v>
       </c>
       <c r="I313">
-        <v>0.7125679545560499</v>
-      </c>
-    </row>
-    <row r="314" spans="1:9">
+        <v>0.71256795455604993</v>
+      </c>
+    </row>
+    <row r="314" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
         <v>321</v>
       </c>
@@ -14125,7 +14151,7 @@
         <v>1352</v>
       </c>
       <c r="E314">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F314">
         <v>1</v>
@@ -14134,13 +14160,13 @@
         <v>0.8</v>
       </c>
       <c r="H314">
-        <v>0.250228576155255</v>
+        <v>0.25022857615525501</v>
       </c>
       <c r="I314">
-        <v>0.5966380706433549</v>
-      </c>
-    </row>
-    <row r="315" spans="1:9">
+        <v>0.59663807064335495</v>
+      </c>
+    </row>
+    <row r="315" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
         <v>322</v>
       </c>
@@ -14154,7 +14180,7 @@
         <v>1353</v>
       </c>
       <c r="E315">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F315">
         <v>1</v>
@@ -14163,13 +14189,13 @@
         <v>0.75</v>
       </c>
       <c r="H315">
-        <v>0.6219022191741638</v>
+        <v>0.62190221917416377</v>
       </c>
       <c r="I315">
-        <v>0.3830462640809889</v>
-      </c>
-    </row>
-    <row r="316" spans="1:9">
+        <v>0.38304626408098891</v>
+      </c>
+    </row>
+    <row r="316" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
         <v>323</v>
       </c>
@@ -14183,7 +14209,7 @@
         <v>1354</v>
       </c>
       <c r="E316">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F316">
         <v>1</v>
@@ -14192,13 +14218,13 @@
         <v>1</v>
       </c>
       <c r="H316">
-        <v>0.3812710884270705</v>
+        <v>0.38127108842707053</v>
       </c>
       <c r="I316">
-        <v>0.3899218914408074</v>
-      </c>
-    </row>
-    <row r="317" spans="1:9">
+        <v>0.38992189144080741</v>
+      </c>
+    </row>
+    <row r="317" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
         <v>324</v>
       </c>
@@ -14212,7 +14238,7 @@
         <v>1355</v>
       </c>
       <c r="E317">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F317">
         <v>1</v>
@@ -14221,13 +14247,13 @@
         <v>1</v>
       </c>
       <c r="H317">
-        <v>0.07576412030503864</v>
+        <v>7.5764120305038637E-2</v>
       </c>
       <c r="I317">
-        <v>0.9646798882796916</v>
-      </c>
-    </row>
-    <row r="318" spans="1:9">
+        <v>0.96467988827969164</v>
+      </c>
+    </row>
+    <row r="318" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
         <v>325</v>
       </c>
@@ -14241,7 +14267,7 @@
         <v>1356</v>
       </c>
       <c r="E318">
-        <v>0.9999999999666667</v>
+        <v>0.99999999996666666</v>
       </c>
       <c r="F318">
         <v>1</v>
@@ -14250,10 +14276,10 @@
         <v>1</v>
       </c>
       <c r="H318">
-        <v>0.5762190915216009</v>
-      </c>
-    </row>
-    <row r="319" spans="1:9">
+        <v>0.57621909152160089</v>
+      </c>
+    </row>
+    <row r="319" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
         <v>326</v>
       </c>
@@ -14267,22 +14293,22 @@
         <v>1357</v>
       </c>
       <c r="E319">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F319">
         <v>1</v>
       </c>
       <c r="G319">
-        <v>0.3333333333333333</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="H319">
-        <v>0.3820968572807873</v>
+        <v>0.38209685728078729</v>
       </c>
       <c r="I319">
-        <v>0.5019997694910093</v>
-      </c>
-    </row>
-    <row r="320" spans="1:9">
+        <v>0.50199976949100933</v>
+      </c>
+    </row>
+    <row r="320" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
         <v>327</v>
       </c>
@@ -14296,7 +14322,7 @@
         <v>1358</v>
       </c>
       <c r="E320">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F320">
         <v>1</v>
@@ -14305,13 +14331,13 @@
         <v>1</v>
       </c>
       <c r="H320">
-        <v>0.5647402091776839</v>
+        <v>0.56474020917768386</v>
       </c>
       <c r="I320">
-        <v>0.83556787809601</v>
-      </c>
-    </row>
-    <row r="321" spans="1:9">
+        <v>0.83556787809600996</v>
+      </c>
+    </row>
+    <row r="321" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
         <v>328</v>
       </c>
@@ -14325,7 +14351,7 @@
         <v>1359</v>
       </c>
       <c r="E321">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F321">
         <v>1</v>
@@ -14334,13 +14360,13 @@
         <v>1</v>
       </c>
       <c r="H321">
-        <v>0.5058411442056588</v>
+        <v>0.50584114420565884</v>
       </c>
       <c r="I321">
-        <v>0.9244295895949162</v>
-      </c>
-    </row>
-    <row r="322" spans="1:9">
+        <v>0.92442958959491617</v>
+      </c>
+    </row>
+    <row r="322" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
         <v>329</v>
       </c>
@@ -14354,7 +14380,7 @@
         <v>1360</v>
       </c>
       <c r="E322">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F322">
         <v>1</v>
@@ -14363,13 +14389,13 @@
         <v>1</v>
       </c>
       <c r="H322">
-        <v>0.5490599946608717</v>
+        <v>0.54905999466087174</v>
       </c>
       <c r="I322">
-        <v>0.9745170605662503</v>
-      </c>
-    </row>
-    <row r="323" spans="1:9">
+        <v>0.97451706056625031</v>
+      </c>
+    </row>
+    <row r="323" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
         <v>330</v>
       </c>
@@ -14383,7 +14409,7 @@
         <v>1361</v>
       </c>
       <c r="E323">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F323">
         <v>1</v>
@@ -14392,13 +14418,13 @@
         <v>1</v>
       </c>
       <c r="H323">
-        <v>0.7626628993773236</v>
+        <v>0.76266289937732357</v>
       </c>
       <c r="I323">
-        <v>0.7312871205906304</v>
-      </c>
-    </row>
-    <row r="324" spans="1:9">
+        <v>0.73128712059063039</v>
+      </c>
+    </row>
+    <row r="324" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
         <v>331</v>
       </c>
@@ -14412,7 +14438,7 @@
         <v>1362</v>
       </c>
       <c r="E324">
-        <v>0.8333333332916666</v>
+        <v>0.83333333329166659</v>
       </c>
       <c r="F324">
         <v>1</v>
@@ -14421,13 +14447,13 @@
         <v>0.4</v>
       </c>
       <c r="H324">
-        <v>0.5031772310709425</v>
+        <v>0.50317723107094248</v>
       </c>
       <c r="I324">
-        <v>0.1630261811327877</v>
-      </c>
-    </row>
-    <row r="325" spans="1:9">
+        <v>0.16302618113278769</v>
+      </c>
+    </row>
+    <row r="325" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
         <v>332</v>
       </c>
@@ -14441,22 +14467,22 @@
         <v>1363</v>
       </c>
       <c r="E325">
-        <v>0.9999999999666667</v>
+        <v>0.99999999996666666</v>
       </c>
       <c r="F325">
         <v>1</v>
       </c>
       <c r="G325">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="H325">
-        <v>0.9113909815288418</v>
+        <v>0.91139098152884179</v>
       </c>
       <c r="I325">
         <v>0.943277610935916</v>
       </c>
     </row>
-    <row r="326" spans="1:9">
+    <row r="326" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
         <v>333</v>
       </c>
@@ -14470,7 +14496,7 @@
         <v>1364</v>
       </c>
       <c r="E326">
-        <v>0.8333333332916666</v>
+        <v>0.83333333329166659</v>
       </c>
       <c r="F326">
         <v>1</v>
@@ -14479,13 +14505,13 @@
         <v>1</v>
       </c>
       <c r="H326">
-        <v>0.5145604553588596</v>
+        <v>0.51456045535885964</v>
       </c>
       <c r="I326">
-        <v>0.5535048330379236</v>
-      </c>
-    </row>
-    <row r="327" spans="1:9">
+        <v>0.55350483303792364</v>
+      </c>
+    </row>
+    <row r="327" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
         <v>334</v>
       </c>
@@ -14499,7 +14525,7 @@
         <v>1365</v>
       </c>
       <c r="E327">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F327">
         <v>1</v>
@@ -14508,13 +14534,13 @@
         <v>1</v>
       </c>
       <c r="H327">
-        <v>0.3837298936222275</v>
+        <v>0.38372989362222748</v>
       </c>
       <c r="I327">
-        <v>0.6899963957243285</v>
-      </c>
-    </row>
-    <row r="328" spans="1:9">
+        <v>0.68999639572432847</v>
+      </c>
+    </row>
+    <row r="328" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
         <v>335</v>
       </c>
@@ -14528,7 +14554,7 @@
         <v>1017</v>
       </c>
       <c r="E328">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F328">
         <v>1</v>
@@ -14537,13 +14563,13 @@
         <v>1</v>
       </c>
       <c r="H328">
-        <v>0.568374845096875</v>
+        <v>0.56837484509687497</v>
       </c>
       <c r="I328">
         <v>1</v>
       </c>
     </row>
-    <row r="329" spans="1:9">
+    <row r="329" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
         <v>336</v>
       </c>
@@ -14566,13 +14592,13 @@
         <v>1</v>
       </c>
       <c r="H329">
-        <v>0.385353936451334</v>
+        <v>0.38535393645133398</v>
       </c>
       <c r="I329">
-        <v>0.8517434641263131</v>
-      </c>
-    </row>
-    <row r="330" spans="1:9">
+        <v>0.85174346412631308</v>
+      </c>
+    </row>
+    <row r="330" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
         <v>337</v>
       </c>
@@ -14586,7 +14612,7 @@
         <v>1367</v>
       </c>
       <c r="E330">
-        <v>0.9999999999666667</v>
+        <v>0.99999999996666666</v>
       </c>
       <c r="F330">
         <v>0</v>
@@ -14595,13 +14621,13 @@
         <v>0</v>
       </c>
       <c r="H330">
-        <v>0.4025929489888651</v>
+        <v>0.40259294898886511</v>
       </c>
       <c r="I330">
         <v>0.1208306278202663</v>
       </c>
     </row>
-    <row r="331" spans="1:9">
+    <row r="331" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
         <v>338</v>
       </c>
@@ -14615,7 +14641,7 @@
         <v>1368</v>
       </c>
       <c r="E331">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F331">
         <v>1</v>
@@ -14624,13 +14650,13 @@
         <v>1</v>
       </c>
       <c r="H331">
-        <v>0.3771592198735232</v>
+        <v>0.37715921987352319</v>
       </c>
       <c r="I331">
-        <v>0.6093336198119194</v>
-      </c>
-    </row>
-    <row r="332" spans="1:9">
+        <v>0.60933361981191936</v>
+      </c>
+    </row>
+    <row r="332" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
         <v>339</v>
       </c>
@@ -14644,7 +14670,7 @@
         <v>1369</v>
       </c>
       <c r="E332">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F332">
         <v>1</v>
@@ -14653,13 +14679,13 @@
         <v>0.75</v>
       </c>
       <c r="H332">
-        <v>0.4609244328655664</v>
+        <v>0.46092443286556639</v>
       </c>
       <c r="I332">
-        <v>0.5917729782370181</v>
-      </c>
-    </row>
-    <row r="333" spans="1:9">
+        <v>0.59177297823701813</v>
+      </c>
+    </row>
+    <row r="333" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
         <v>340</v>
       </c>
@@ -14673,7 +14699,7 @@
         <v>1370</v>
       </c>
       <c r="E333">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F333">
         <v>1</v>
@@ -14685,10 +14711,10 @@
         <v>0.2184977833126803</v>
       </c>
       <c r="I333">
-        <v>0.971685690696567</v>
-      </c>
-    </row>
-    <row r="334" spans="1:9">
+        <v>0.97168569069656696</v>
+      </c>
+    </row>
+    <row r="334" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
         <v>341</v>
       </c>
@@ -14711,13 +14737,13 @@
         <v>1</v>
       </c>
       <c r="H334">
-        <v>0.3696488841135426</v>
+        <v>0.36964888411354258</v>
       </c>
       <c r="I334">
         <v>0.991350820240956</v>
       </c>
     </row>
-    <row r="335" spans="1:9">
+    <row r="335" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
         <v>342</v>
       </c>
@@ -14740,13 +14766,13 @@
         <v>1</v>
       </c>
       <c r="H335">
-        <v>0.4913172318198407</v>
+        <v>0.49131723181984072</v>
       </c>
       <c r="I335">
         <v>1</v>
       </c>
     </row>
-    <row r="336" spans="1:9">
+    <row r="336" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
         <v>343</v>
       </c>
@@ -14760,7 +14786,7 @@
         <v>1372</v>
       </c>
       <c r="E336">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F336">
         <v>1</v>
@@ -14769,13 +14795,13 @@
         <v>1</v>
       </c>
       <c r="H336">
-        <v>0.6407992194867109</v>
+        <v>0.64079921948671092</v>
       </c>
       <c r="I336">
-        <v>0.3884656668413551</v>
-      </c>
-    </row>
-    <row r="337" spans="1:9">
+        <v>0.38846566684135508</v>
+      </c>
+    </row>
+    <row r="337" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
         <v>344</v>
       </c>
@@ -14798,13 +14824,13 @@
         <v>0</v>
       </c>
       <c r="H337">
-        <v>0.603338600742626</v>
+        <v>0.60333860074262602</v>
       </c>
       <c r="I337">
-        <v>0.1675332235280469</v>
-      </c>
-    </row>
-    <row r="338" spans="1:9">
+        <v>0.16753322352804689</v>
+      </c>
+    </row>
+    <row r="338" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
         <v>345</v>
       </c>
@@ -14818,7 +14844,7 @@
         <v>1374</v>
       </c>
       <c r="E338">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F338">
         <v>1</v>
@@ -14827,13 +14853,13 @@
         <v>1</v>
       </c>
       <c r="H338">
-        <v>0.3541108452301526</v>
+        <v>0.35411084523015263</v>
       </c>
       <c r="I338">
-        <v>0.9900800346502188</v>
-      </c>
-    </row>
-    <row r="339" spans="1:9">
+        <v>0.99008003465021877</v>
+      </c>
+    </row>
+    <row r="339" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
         <v>346</v>
       </c>
@@ -14847,7 +14873,7 @@
         <v>1375</v>
       </c>
       <c r="E339">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F339">
         <v>1</v>
@@ -14856,13 +14882,13 @@
         <v>0.5</v>
       </c>
       <c r="H339">
-        <v>0.4987175108205115</v>
+        <v>0.49871751082051152</v>
       </c>
       <c r="I339">
-        <v>0.9745669556943858</v>
-      </c>
-    </row>
-    <row r="340" spans="1:9">
+        <v>0.97456695569438578</v>
+      </c>
+    </row>
+    <row r="340" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
         <v>347</v>
       </c>
@@ -14876,7 +14902,7 @@
         <v>1376</v>
       </c>
       <c r="E340">
-        <v>0.5833333333041666</v>
+        <v>0.58333333330416659</v>
       </c>
       <c r="F340">
         <v>0</v>
@@ -14888,10 +14914,10 @@
         <v>0.5404753784037557</v>
       </c>
       <c r="I340">
-        <v>0.1333671814379088</v>
-      </c>
-    </row>
-    <row r="341" spans="1:9">
+        <v>0.13336718143790879</v>
+      </c>
+    </row>
+    <row r="341" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
         <v>348</v>
       </c>
@@ -14905,7 +14931,7 @@
         <v>1377</v>
       </c>
       <c r="E341">
-        <v>0.9999999999666667</v>
+        <v>0.99999999996666666</v>
       </c>
       <c r="F341">
         <v>1</v>
@@ -14914,13 +14940,13 @@
         <v>0.75</v>
       </c>
       <c r="H341">
-        <v>0.4086985454453105</v>
+        <v>0.40869854544531048</v>
       </c>
       <c r="I341">
-        <v>0.5604276897753691</v>
-      </c>
-    </row>
-    <row r="342" spans="1:9">
+        <v>0.56042768977536905</v>
+      </c>
+    </row>
+    <row r="342" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
         <v>349</v>
       </c>
@@ -14934,7 +14960,7 @@
         <v>1378</v>
       </c>
       <c r="E342">
-        <v>0.9999999999666667</v>
+        <v>0.99999999996666666</v>
       </c>
       <c r="F342">
         <v>1</v>
@@ -14943,13 +14969,13 @@
         <v>1</v>
       </c>
       <c r="H342">
-        <v>0.505000913634593</v>
+        <v>0.50500091363459298</v>
       </c>
       <c r="I342">
-        <v>0.1539651802381237</v>
-      </c>
-    </row>
-    <row r="343" spans="1:9">
+        <v>0.15396518023812369</v>
+      </c>
+    </row>
+    <row r="343" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
         <v>350</v>
       </c>
@@ -14972,13 +14998,13 @@
         <v>1</v>
       </c>
       <c r="H343">
-        <v>0.5282328262175309</v>
+        <v>0.52823282621753087</v>
       </c>
       <c r="I343">
-        <v>0.4987698389318679</v>
-      </c>
-    </row>
-    <row r="344" spans="1:9">
+        <v>0.49876983893186788</v>
+      </c>
+    </row>
+    <row r="344" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
         <v>351</v>
       </c>
@@ -14992,7 +15018,7 @@
         <v>1380</v>
       </c>
       <c r="E344">
-        <v>0.9999999999666667</v>
+        <v>0.99999999996666666</v>
       </c>
       <c r="F344">
         <v>1</v>
@@ -15001,13 +15027,13 @@
         <v>1</v>
       </c>
       <c r="H344">
-        <v>0.7902198230603968</v>
+        <v>0.79021982306039684</v>
       </c>
       <c r="I344">
-        <v>0.8542433371574005</v>
-      </c>
-    </row>
-    <row r="345" spans="1:9">
+        <v>0.85424333715740053</v>
+      </c>
+    </row>
+    <row r="345" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
         <v>352</v>
       </c>
@@ -15030,13 +15056,13 @@
         <v>0.4</v>
       </c>
       <c r="H345">
-        <v>0.5820907445673186</v>
+        <v>0.58209074456731857</v>
       </c>
       <c r="I345">
-        <v>0.7792756798611462</v>
-      </c>
-    </row>
-    <row r="346" spans="1:9">
+        <v>0.77927567986114621</v>
+      </c>
+    </row>
+    <row r="346" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
         <v>353</v>
       </c>
@@ -15050,7 +15076,7 @@
         <v>1382</v>
       </c>
       <c r="E346">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F346">
         <v>1</v>
@@ -15059,13 +15085,13 @@
         <v>1</v>
       </c>
       <c r="H346">
-        <v>0.6821833164001763</v>
+        <v>0.68218331640017627</v>
       </c>
       <c r="I346">
-        <v>0.9786356165229014</v>
-      </c>
-    </row>
-    <row r="347" spans="1:9">
+        <v>0.97863561652290143</v>
+      </c>
+    </row>
+    <row r="347" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
         <v>354</v>
       </c>
@@ -15079,7 +15105,7 @@
         <v>1036</v>
       </c>
       <c r="E347">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F347">
         <v>1</v>
@@ -15088,13 +15114,13 @@
         <v>1</v>
       </c>
       <c r="H347">
-        <v>0.2120886233741379</v>
+        <v>0.21208862337413789</v>
       </c>
       <c r="I347">
         <v>1</v>
       </c>
     </row>
-    <row r="348" spans="1:9">
+    <row r="348" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
         <v>355</v>
       </c>
@@ -15108,7 +15134,7 @@
         <v>1383</v>
       </c>
       <c r="E348">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F348">
         <v>1</v>
@@ -15117,13 +15143,13 @@
         <v>0.75</v>
       </c>
       <c r="H348">
-        <v>0.4704043326479053</v>
+        <v>0.47040433264790532</v>
       </c>
       <c r="I348">
-        <v>0.6391223686787395</v>
-      </c>
-    </row>
-    <row r="349" spans="1:9">
+        <v>0.63912236867873951</v>
+      </c>
+    </row>
+    <row r="349" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A349" t="s">
         <v>356</v>
       </c>
@@ -15137,7 +15163,7 @@
         <v>1384</v>
       </c>
       <c r="E349">
-        <v>0.8333333332916666</v>
+        <v>0.83333333329166659</v>
       </c>
       <c r="F349">
         <v>1</v>
@@ -15146,13 +15172,13 @@
         <v>1</v>
       </c>
       <c r="H349">
-        <v>0.4292466486150102</v>
+        <v>0.42924664861501022</v>
       </c>
       <c r="I349">
-        <v>0.9790570711970629</v>
-      </c>
-    </row>
-    <row r="350" spans="1:9">
+        <v>0.97905707119706287</v>
+      </c>
+    </row>
+    <row r="350" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
         <v>357</v>
       </c>
@@ -15166,7 +15192,7 @@
         <v>1385</v>
       </c>
       <c r="E350">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F350">
         <v>1</v>
@@ -15175,13 +15201,13 @@
         <v>1</v>
       </c>
       <c r="H350">
-        <v>0.3719560093722526</v>
+        <v>0.37195600937225259</v>
       </c>
       <c r="I350">
-        <v>0.9808693837673113</v>
-      </c>
-    </row>
-    <row r="351" spans="1:9">
+        <v>0.98086938376731125</v>
+      </c>
+    </row>
+    <row r="351" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
         <v>358</v>
       </c>
@@ -15204,13 +15230,13 @@
         <v>0</v>
       </c>
       <c r="H351">
-        <v>0.7000139058615925</v>
+        <v>0.70001390586159251</v>
       </c>
       <c r="I351">
-        <v>0.5845874801559878</v>
-      </c>
-    </row>
-    <row r="352" spans="1:9">
+        <v>0.58458748015598783</v>
+      </c>
+    </row>
+    <row r="352" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
         <v>359</v>
       </c>
@@ -15224,7 +15250,7 @@
         <v>1387</v>
       </c>
       <c r="E352">
-        <v>0.9999999999666667</v>
+        <v>0.99999999996666666</v>
       </c>
       <c r="F352">
         <v>1</v>
@@ -15233,13 +15259,13 @@
         <v>1</v>
       </c>
       <c r="H352">
-        <v>0.5264666822727734</v>
+        <v>0.52646668227277338</v>
       </c>
       <c r="I352">
-        <v>0.9852434988782621</v>
-      </c>
-    </row>
-    <row r="353" spans="1:9">
+        <v>0.98524349887826213</v>
+      </c>
+    </row>
+    <row r="353" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A353" t="s">
         <v>360</v>
       </c>
@@ -15253,22 +15279,22 @@
         <v>1388</v>
       </c>
       <c r="E353">
-        <v>0.9999999999666667</v>
+        <v>0.99999999996666666</v>
       </c>
       <c r="F353">
         <v>1</v>
       </c>
       <c r="G353">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="H353">
-        <v>0.4588605526010645</v>
+        <v>0.45886055260106451</v>
       </c>
       <c r="I353">
-        <v>0.6983254255426923</v>
-      </c>
-    </row>
-    <row r="354" spans="1:9">
+        <v>0.69832542554269228</v>
+      </c>
+    </row>
+    <row r="354" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A354" t="s">
         <v>361</v>
       </c>
@@ -15291,13 +15317,13 @@
         <v>1</v>
       </c>
       <c r="H354">
-        <v>0.8419888839390853</v>
+        <v>0.84198888393908533</v>
       </c>
       <c r="I354">
-        <v>0.9930670134744202</v>
-      </c>
-    </row>
-    <row r="355" spans="1:9">
+        <v>0.99306701347442017</v>
+      </c>
+    </row>
+    <row r="355" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A355" t="s">
         <v>362</v>
       </c>
@@ -15311,7 +15337,7 @@
         <v>1390</v>
       </c>
       <c r="E355">
-        <v>0.9999999999666667</v>
+        <v>0.99999999996666666</v>
       </c>
       <c r="F355">
         <v>1</v>
@@ -15320,13 +15346,13 @@
         <v>1</v>
       </c>
       <c r="H355">
-        <v>0.7495437567373086</v>
+        <v>0.74954375673730855</v>
       </c>
       <c r="I355">
-        <v>0.5857893772703313</v>
-      </c>
-    </row>
-    <row r="356" spans="1:9">
+        <v>0.58578937727033131</v>
+      </c>
+    </row>
+    <row r="356" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A356" t="s">
         <v>363</v>
       </c>
@@ -15340,7 +15366,7 @@
         <v>1391</v>
       </c>
       <c r="E356">
-        <v>0.9999999999</v>
+        <v>0.99999999989999999</v>
       </c>
       <c r="F356">
         <v>1</v>
@@ -15349,13 +15375,14 @@
         <v>1</v>
       </c>
       <c r="H356">
-        <v>0.4176910524201394</v>
+        <v>0.41769105242013937</v>
       </c>
       <c r="I356">
-        <v>0.8674097842403332</v>
+        <v>0.86740978424033321</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>